--- a/src/attributions/attributions_saliency_traj_488.xlsx
+++ b/src/attributions/attributions_saliency_traj_488.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.208247497677803</v>
+        <v>0.004319922532886267</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1159680187702179</v>
+        <v>0.04090705513954163</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3101639151573181</v>
+        <v>0.2549178898334503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2673531770706177</v>
+        <v>0.2642623782157898</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05140402168035507</v>
+        <v>0.13552425801754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01412583142518997</v>
+        <v>0.05438815057277679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006352514028549194</v>
+        <v>0.0708746463060379</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1638874113559723</v>
+        <v>0.02073831856250763</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02206742390990257</v>
+        <v>0.04069947823882103</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2695512771606445</v>
+        <v>0.01864773407578468</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1347727477550507</v>
+        <v>0.01554082427173853</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2510432004928589</v>
+        <v>0.2024601697921753</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2529127895832062</v>
+        <v>0.2391704320907593</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1808318197727203</v>
+        <v>0.1537144780158997</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001386679010465741</v>
+        <v>0.0480426624417305</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06142137199640274</v>
+        <v>0.04202676564455032</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1623091846704483</v>
+        <v>0.1524202823638916</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04313863068819046</v>
+        <v>0.04657990485429764</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08081918954849243</v>
+        <v>0.06149580702185631</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00744921900331974</v>
+        <v>0.00190589833073318</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02078699506819248</v>
+        <v>0.06413467973470688</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0220630094408989</v>
+        <v>0.100611686706543</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1147974357008934</v>
+        <v>0.0464717224240303</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05399243161082268</v>
+        <v>0.1428641974925995</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02134856954216957</v>
+        <v>0.0555182546377182</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1343542188405991</v>
+        <v>0.01156822126358747</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01992221921682358</v>
+        <v>0.009005469270050526</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02029991336166859</v>
+        <v>0.06032584235072136</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.07928933203220367</v>
+        <v>0.04878147691488266</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01405772473663092</v>
+        <v>0.04947244003415108</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.06146138161420822</v>
+        <v>0.03767632320523262</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05228303745388985</v>
+        <v>0.05869217216968536</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.005813817959278822</v>
+        <v>0.09590565413236618</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02857189439237118</v>
+        <v>0.04006225615739822</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.02805548161268234</v>
+        <v>0.1440861225128174</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03145720809698105</v>
+        <v>0.1087331250309944</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0234176479279995</v>
+        <v>0.04730679094791412</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04926224052906036</v>
+        <v>0.010022958740592</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.01246000919491053</v>
+        <v>0.0748874619603157</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03343306481838226</v>
+        <v>0.1706478595733643</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.03590293973684311</v>
+        <v>0.003530321642756462</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.03929072618484497</v>
+        <v>0.01813839375972748</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.04009855538606644</v>
+        <v>0.1172501444816589</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01532574743032455</v>
+        <v>0.001308579463511705</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.01265248283743858</v>
+        <v>0.02239323779940605</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.009793446399271488</v>
+        <v>0.04806315153837204</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.07012958824634552</v>
+        <v>0.0475865826010704</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1960477828979492</v>
+        <v>0.2123890072107315</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2467475086450577</v>
+        <v>0.297979474067688</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03490498289465904</v>
+        <v>0.1026014611124992</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.07249460369348526</v>
+        <v>0.04875857010483742</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.06796073168516159</v>
+        <v>0.1313218623399734</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1324825435876846</v>
+        <v>0.03277943655848503</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.04630765318870544</v>
+        <v>0.098194420337677</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2229171395301819</v>
+        <v>0.07598432898521423</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09527429938316345</v>
+        <v>0.04855813086032867</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.03888291120529175</v>
+        <v>0.000293782475637272</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.008884545415639877</v>
+        <v>0.1985998451709747</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1699802428483963</v>
+        <v>0.01822919771075249</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.01211372949182987</v>
+        <v>0.1630623787641525</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1601853221654892</v>
+        <v>0.1021972447633743</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.2828366160392761</v>
+        <v>0.06186360865831375</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02582294493913651</v>
+        <v>0.1593720316886902</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.004347633570432663</v>
+        <v>0.01146412640810013</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.04183514788746834</v>
+        <v>0.04810372367501259</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.06267151236534119</v>
+        <v>0.04938629269599915</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.08578053116798401</v>
+        <v>0.02189446799457073</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1116752624511719</v>
+        <v>0.06660072505474091</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01703164726495743</v>
+        <v>0.0150003544986248</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.06373012810945511</v>
+        <v>0.002296310849487782</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.02305747754871845</v>
+        <v>0.0522812120616436</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.03530779853463173</v>
+        <v>0.0004852591082453728</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0194852389395237</v>
+        <v>0.02709200233221054</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.08339714258909225</v>
+        <v>0.05167575180530548</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.09696178883314133</v>
+        <v>0.1506805717945099</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1251496374607086</v>
+        <v>0.3067535758018494</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.06534678488969803</v>
+        <v>0.03223754465579987</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.001571961911395192</v>
+        <v>0.03040634281933308</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0559014230966568</v>
+        <v>0.07373130321502686</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1530703902244568</v>
+        <v>0.01090800948441029</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05398218333721161</v>
+        <v>0.02039033174514771</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.04935917630791664</v>
+        <v>0.007681288756430149</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.04440641775727272</v>
+        <v>0.03344004601240158</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.06588437408208847</v>
+        <v>0.05937943235039711</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.05457496643066406</v>
+        <v>0.09733676165342331</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.04292235523462296</v>
+        <v>0.008822830393910408</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.03474895283579826</v>
+        <v>0.03410722315311432</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.02592432498931885</v>
+        <v>0.009656647220253944</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.03315357491374016</v>
+        <v>0.04062195867300034</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.03175805509090424</v>
+        <v>0.01587241142988205</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1034502759575844</v>
+        <v>0.01920182816684246</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.04686251282691956</v>
+        <v>0.008826214820146561</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.009018506854772568</v>
+        <v>0.06345877051353455</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02472108975052834</v>
+        <v>0.0667460709810257</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.08418140560388565</v>
+        <v>0.1276426464319229</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.002451628446578979</v>
+        <v>0.03060995601117611</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.008037533611059189</v>
+        <v>0.0197721179574728</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.08732429146766663</v>
+        <v>0.01619177870452404</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.06224093586206436</v>
+        <v>0.06911846995353699</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.05044552683830261</v>
+        <v>0.01464890688657761</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.02106583490967751</v>
+        <v>0.002715941052883863</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.03644838184118271</v>
+        <v>0.05444395169615746</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0364224836230278</v>
+        <v>0.1058104038238525</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.04693259298801422</v>
+        <v>0.03268866613507271</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.02138589136302471</v>
+        <v>0.04304426908493042</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.007021590135991573</v>
+        <v>0.02115553244948387</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.02046060748398304</v>
+        <v>0.03375446796417236</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.03273627534508705</v>
+        <v>0.02017761021852493</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.007035363465547562</v>
+        <v>0.004182303324341774</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1737668663263321</v>
+        <v>0.05262753367424011</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.05696040019392967</v>
+        <v>0.15159010887146</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.05443065240979195</v>
+        <v>0.1280492544174194</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01938087120652199</v>
+        <v>0.02543053030967712</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.1681064516305923</v>
+        <v>0.06797376275062561</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.1626039445400238</v>
+        <v>0.01330138742923737</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.0008842676179483533</v>
+        <v>0.1913544833660126</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.02015746384859085</v>
+        <v>0.04503726959228516</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.01139754988253117</v>
+        <v>0.0842253640294075</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02008863165974617</v>
+        <v>0.03023533523082733</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.06486896425485611</v>
+        <v>0.02034086734056473</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.006827662698924541</v>
+        <v>0.08094251900911331</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.05627918615937233</v>
+        <v>0.03122711926698685</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.02041912451386452</v>
+        <v>0.01105095632374287</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.06359024345874786</v>
+        <v>0.03383100032806396</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.03404074534773827</v>
+        <v>0.01669842377305031</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.02843524515628815</v>
+        <v>0.1017841324210167</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.02594609744846821</v>
+        <v>0.03087402135133743</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.002550018951296806</v>
+        <v>0.04600128158926964</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.03887666761875153</v>
+        <v>0.0136592136695981</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.02053104527294636</v>
+        <v>0.01762813702225685</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002066349377855659</v>
+        <v>0.0288093127310276</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.1171456053853035</v>
+        <v>0.1184633448719978</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01356273982673883</v>
+        <v>0.03901300206780434</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.08089405298233032</v>
+        <v>0.09496525675058365</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.07341336458921432</v>
+        <v>0.1009689271450043</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.04656608775258064</v>
+        <v>0.03867781162261963</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0246705561876297</v>
+        <v>0.01396516710519791</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.06640778481960297</v>
+        <v>0.04574636369943619</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.07223419845104218</v>
+        <v>0.0742468535900116</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.007292954251170158</v>
+        <v>0.06881888210773468</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01713080890476704</v>
+        <v>0.03959833458065987</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0290644820779562</v>
+        <v>0.02534579858183861</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.02690334990620613</v>
+        <v>0.02639379352331161</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.06442006677389145</v>
+        <v>0.01709248498082161</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.02457329258322716</v>
+        <v>0.03225719928741455</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.009937326423823833</v>
+        <v>0.0470932200551033</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.07207620143890381</v>
+        <v>0.01236921362578869</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.04011711105704308</v>
+        <v>0.0680229514837265</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.004727696999907494</v>
+        <v>0.03877337649464607</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.01887491531670094</v>
+        <v>0.1051956340670586</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.01692561432719231</v>
+        <v>0.02548200823366642</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.1025870218873024</v>
+        <v>0.0512867234647274</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003511398332193494</v>
+        <v>0.03542251884937286</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.04442343860864639</v>
+        <v>0.01924391835927963</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.02666733600199223</v>
+        <v>0.03672948852181435</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.04927292093634605</v>
+        <v>0.05555800721049309</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.03991725295782089</v>
+        <v>0.1054374501109123</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02758490480482578</v>
+        <v>0.004059670493006706</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.03282539173960686</v>
+        <v>0.01958433166146278</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.015323999337852</v>
+        <v>0.02625489421188831</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.01402838807553053</v>
+        <v>0.06204685196280479</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.04604325070977211</v>
+        <v>0.01230026874691248</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.02372065931558609</v>
+        <v>0.003647191449999809</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03561581671237946</v>
+        <v>0.02721334621310234</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0215122252702713</v>
+        <v>0.1005767583847046</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.05942504853010178</v>
+        <v>0.06849660724401474</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.06041119247674942</v>
+        <v>0.03590147569775581</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.07611170411109924</v>
+        <v>0.08929788321256638</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.02044665813446045</v>
+        <v>0.007089925929903984</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.03640715032815933</v>
+        <v>0.01113545522093773</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.08895132690668106</v>
+        <v>0.07497150450944901</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.1270881593227386</v>
+        <v>0.06378235667943954</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.06088782846927643</v>
+        <v>0.04282218217849731</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.1704387366771698</v>
+        <v>0.07440754771232605</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.07000494748353958</v>
+        <v>0.02052577584981918</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.04021414369344711</v>
+        <v>0.03398096561431885</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0529526025056839</v>
+        <v>0.022451376542449</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.02153968065977097</v>
+        <v>0.1319494098424911</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.007904341444373131</v>
+        <v>0.01215830631554127</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.05021362751722336</v>
+        <v>0.01803520508110523</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.03629007935523987</v>
+        <v>0.007182488217949867</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.002548801712691784</v>
+        <v>0.1042367443442345</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.04557998105883598</v>
+        <v>0.09192945808172226</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.08267185091972351</v>
+        <v>0.08114220201969147</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0681847482919693</v>
+        <v>0.05521947145462036</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.1018497720360756</v>
+        <v>0.06124675273895264</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0055819321423769</v>
+        <v>0.08324629068374634</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.02041137591004372</v>
+        <v>0.05174916982650757</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.003548723179847002</v>
+        <v>0.003834852483123541</v>
       </c>
     </row>
     <row r="3">
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0002478035748936236</v>
+        <v>0.0001864600635599345</v>
       </c>
       <c r="B4" t="n">
-        <v>0.005808106623589993</v>
+        <v>0.0003346151788718998</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001235956908203661</v>
+        <v>4.729015563498251e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002113586291670799</v>
+        <v>4.049330163979903e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008459917269647121</v>
+        <v>0.0001168340604635887</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002439242321997881</v>
+        <v>0.0002510457998141646</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007450926350429654</v>
+        <v>0.0001608762540854514</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008266164222732186</v>
+        <v>7.290870416909456e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001397200161591172</v>
+        <v>7.92356368037872e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000785685027949512</v>
+        <v>0.0001853007997851819</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003931000828742981</v>
+        <v>0.0004198371898382902</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005092821083962917</v>
+        <v>8.94878976396285e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001783257233910263</v>
+        <v>3.160516280331649e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007511736359447241</v>
+        <v>4.661378625314683e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003062456613406539</v>
+        <v>0.0002214103151345626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001305756741203368</v>
+        <v>0.0001202675703098066</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0002350962313357741</v>
+        <v>3.533928975230083e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001307509373873472</v>
+        <v>0.00015062557940837</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001882693031802773</v>
+        <v>1.516756128694396e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001641867798753083</v>
+        <v>2.646661050675903e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0002801310329232365</v>
+        <v>7.019596523605287e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>8.57541526784189e-05</v>
+        <v>6.011568257235922e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002249083336209878</v>
+        <v>5.11806138092652e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001964723924174905</v>
+        <v>1.553508081997279e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004494498134590685</v>
+        <v>9.032365596794989e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000185780692845583</v>
+        <v>0.0001000756092253141</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002546929463278502</v>
+        <v>5.674684507539496e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.468227365985513e-05</v>
+        <v>6.451966328313574e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001085739582777023</v>
+        <v>1.643711038923357e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006033367244526744</v>
+        <v>7.33824199414812e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0004840200999751687</v>
+        <v>0.0001154474884970114</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0005700185429304838</v>
+        <v>0.0001044430828187615</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001092933584004641</v>
+        <v>9.579002835380379e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000870496965944767</v>
+        <v>1.153251832874957e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0007571254391223192</v>
+        <v>0.00018530577654019</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.000156490714289248</v>
+        <v>4.584277485264465e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0002256108273286372</v>
+        <v>6.115960422903299e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001821270561777055</v>
+        <v>4.253214865457267e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0004945353139191866</v>
+        <v>5.413089820649475e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000602812971919775</v>
+        <v>7.907523104222491e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.884462471934967e-05</v>
+        <v>9.282499377150089e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0004947695997543633</v>
+        <v>2.624270200612955e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0004460255149751902</v>
+        <v>3.986414594692178e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0003847689367830753</v>
+        <v>7.445787196047604e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0004614118079189211</v>
+        <v>5.507103924173862e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0007784877670928836</v>
+        <v>0.000144884514156729</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004668400157243013</v>
+        <v>0.0002310788695467636</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0006736842915415764</v>
+        <v>5.131438956595957e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.044464392587543e-06</v>
+        <v>1.612411688256543e-05</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.003337404690682888</v>
+        <v>3.798806210397743e-05</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001810718211345375</v>
+        <v>0.00010827664664248</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001366237294860184</v>
+        <v>1.233471084560733e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0003203331143595278</v>
+        <v>9.075715934159234e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0004616287769749761</v>
+        <v>4.805496064363979e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007674271473661065</v>
+        <v>4.846388037549332e-07</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0004400843172334135</v>
+        <v>6.418178963940591e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0004322709864936769</v>
+        <v>4.338505459600128e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00137634202837944</v>
+        <v>1.899382914416492e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005046256817877293</v>
+        <v>6.701211532345042e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006206084508448839</v>
+        <v>0.000120258962851949</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001494952826760709</v>
+        <v>9.456903353566304e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0003076858120039105</v>
+        <v>3.337593807373196e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00177838874515146</v>
+        <v>6.849789497209713e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006988664390519261</v>
+        <v>2.213345851487247e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0009676717454567552</v>
+        <v>1.913649430207442e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0004126616986468434</v>
+        <v>5.780324499937706e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0002193761611124501</v>
+        <v>1.163765773526393e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001011722953990102</v>
+        <v>1.07193918665871e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001039233990013599</v>
+        <v>2.33165810641367e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001244060229510069</v>
+        <v>0.0001341653551207855</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0004820781759917736</v>
+        <v>1.883996446849778e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.502607483416796e-05</v>
+        <v>9.212010627379641e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0006646168185397983</v>
+        <v>5.620864249067381e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002957914024591446</v>
+        <v>0.0001781754835974425</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.001596714835613966</v>
+        <v>5.259284080239013e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0005440629902295768</v>
+        <v>9.488327486906201e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002054483164101839</v>
+        <v>1.598556991666555e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.000699895725119859</v>
+        <v>8.294748840853572e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0005781951476819813</v>
+        <v>1.399673601554241e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0001301343727391213</v>
+        <v>3.270492015872151e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0001002478384179994</v>
+        <v>5.443980262498371e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.780013114213943e-06</v>
+        <v>4.974293551640585e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0008941173437051475</v>
+        <v>7.960202492540702e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.880372448998969e-05</v>
+        <v>1.341211827821098e-06</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.000552453740965575</v>
+        <v>2.079478326777462e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009811641648411751</v>
+        <v>6.053153629181907e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0006287097348831594</v>
+        <v>6.208351987879723e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0006174924783408642</v>
+        <v>5.793165473733097e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>5.448608135338873e-05</v>
+        <v>4.319422714615939e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.070371167268604e-05</v>
+        <v>1.650067679292988e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001029656152240932</v>
+        <v>1.992758916458115e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0001898882183013484</v>
+        <v>5.630816303892061e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.944088090676814e-05</v>
+        <v>5.348955892259255e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0008849374135024846</v>
+        <v>7.932950393296778e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001228167209774256</v>
+        <v>6.415175448637456e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0001682357833487913</v>
+        <v>6.353243225021288e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001315272878855467</v>
+        <v>2.569650678196922e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001541833393275738</v>
+        <v>2.26409756578505e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0005294486181810498</v>
+        <v>3.916265632142313e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>5.290409899316728e-05</v>
+        <v>3.626609031925909e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.000440270610852167</v>
+        <v>7.77391396695748e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0001867994869826362</v>
+        <v>3.898856448358856e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0007058125920593739</v>
+        <v>1.993957812373992e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001003247685730457</v>
+        <v>4.559590161079541e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.000836182211060077</v>
+        <v>6.231518636923283e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.000387585605494678</v>
+        <v>2.791140650515445e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0002483076532371342</v>
+        <v>1.318469003308564e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002808246063068509</v>
+        <v>1.904885357362218e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001004091114737093</v>
+        <v>3.99357159039937e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001059341710060835</v>
+        <v>0.0001124531481764279</v>
       </c>
       <c r="DG4" t="n">
-        <v>6.027744530001655e-05</v>
+        <v>0.0001161257459898479</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.00106123392470181</v>
+        <v>2.428283733024728e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0006901996675878763</v>
+        <v>0.0001527271379018202</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002685062354430556</v>
+        <v>0.0002455625217407942</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001180710853077471</v>
+        <v>1.504822648712434e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0005765164969488978</v>
+        <v>2.401377969363239e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001233188784681261</v>
+        <v>6.913923425599933e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>7.751304656267166e-05</v>
+        <v>3.420580105739646e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>5.279688048176467e-05</v>
+        <v>6.499174924101681e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0002089474292006344</v>
+        <v>6.582136848010123e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001601597759872675</v>
+        <v>5.541044811252505e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0001571292523294687</v>
+        <v>3.176774771418422e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001592054381035268</v>
+        <v>0.0001493977470090613</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0009383888682350516</v>
+        <v>1.638939102122094e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0003498286241665483</v>
+        <v>0.0001283677120227367</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0002149021020159125</v>
+        <v>3.445022230152972e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.014580629998818e-05</v>
+        <v>3.944411582779139e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000130825734231621</v>
+        <v>5.055526344222017e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0006775489309802651</v>
+        <v>7.596339855808765e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.00105767697095871</v>
+        <v>6.994733121246099e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.000690933782607317</v>
+        <v>6.534989370265976e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0005341256037354469</v>
+        <v>0.0001059105561580509</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0004896789323538542</v>
+        <v>7.36284982849611e-06</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00019646534929052</v>
+        <v>5.957399116596207e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0004087289271410555</v>
+        <v>8.760458877077326e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0004765365738421679</v>
+        <v>4.828989403904416e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0005745437811128795</v>
+        <v>2.023728711719741e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>4.407097367220558e-05</v>
+        <v>4.765933408634737e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0003651062725111842</v>
+        <v>1.056960536516272e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001298334100283682</v>
+        <v>8.104721928248182e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0002904750872403383</v>
+        <v>2.234341991425026e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0008355429163202643</v>
+        <v>3.520911923260428e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>6.242937524802983e-05</v>
+        <v>2.915088953159284e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004373386909719557</v>
+        <v>7.602858204336371e-06</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002325428067706525</v>
+        <v>4.855994484387338e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0004473466251511127</v>
+        <v>4.004163201898336e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0009531775140203536</v>
+        <v>2.25885996769648e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.000726081314496696</v>
+        <v>8.78783903317526e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0006171650602482259</v>
+        <v>0.0001171363546745852</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001369691919535398</v>
+        <v>0.0001464798697270453</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0001250973728019744</v>
+        <v>5.536973731068429e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0007211423944681883</v>
+        <v>4.538600842352025e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0004810002574231476</v>
+        <v>5.779779166914523e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001218630204675719</v>
+        <v>4.493990854825824e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0004607573209796101</v>
+        <v>9.241861698683351e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.20192814595066e-05</v>
+        <v>9.642158147471491e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0008021427784115076</v>
+        <v>1.166239599115215e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0008995046373456717</v>
+        <v>6.867283082101494e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0008509288891218603</v>
+        <v>6.333108467515558e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0005950480699539185</v>
+        <v>5.081066046841443e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>4.663377330871299e-05</v>
+        <v>7.94887455413118e-07</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0001233627262990922</v>
+        <v>4.043597982672509e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0002864249981939793</v>
+        <v>1.494076241215225e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0008989029447548091</v>
+        <v>0.0001594075292814523</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.000749919330701232</v>
+        <v>6.969059904804453e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001562897581607103</v>
+        <v>1.540001903777011e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.803066308842972e-05</v>
+        <v>6.079683771531563e-06</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0002046012668870389</v>
+        <v>0.0001373090053675696</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.001034646993502975</v>
+        <v>3.606894460972399e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0007653674692846835</v>
+        <v>0.0001527882559457794</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0008961115963757038</v>
+        <v>8.839373185764998e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0005175592959858477</v>
+        <v>5.298243922879919e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001830282155424356</v>
+        <v>3.083417323068716e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0005412268219515681</v>
+        <v>0.000179855473106727</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.002172750886529684</v>
+        <v>0.0001330498780589551</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001320422161370516</v>
+        <v>3.499378362903371e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0003620662610046566</v>
+        <v>5.017947478336282e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0008885777788236737</v>
+        <v>2.73704335995717e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.000322145817335695</v>
+        <v>4.59570437669754e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0003805567394010723</v>
+        <v>2.677055999811273e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0005831597372889519</v>
+        <v>7.249240297824144e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>3.916992136510089e-05</v>
+        <v>7.824472413631156e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001132745412178338</v>
+        <v>5.106157914269716e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0006462712772190571</v>
+        <v>3.281226599938236e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0006990599795244634</v>
+        <v>0.0001139920859714039</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0006751207401975989</v>
+        <v>8.781015640124679e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001105461618863046</v>
+        <v>2.855635466403328e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0001314391265623271</v>
+        <v>4.536798587650992e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.001068950863555074</v>
+        <v>0.0001506583503214642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.004803136456757784</v>
+        <v>0.04554925858974457</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04361432418227196</v>
+        <v>0.7650152444839478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008509906474500895</v>
+        <v>0.4098747074604034</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01704936847090721</v>
+        <v>0.6296545267105103</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03215239942073822</v>
+        <v>0.3073623180389404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01957856304943562</v>
+        <v>0.03259254992008209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003301253891550004</v>
+        <v>0.5024657249450684</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004174097441136837</v>
+        <v>0.2104456573724747</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01495240442454815</v>
+        <v>0.04559047147631645</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002516728127375245</v>
+        <v>0.0417640432715416</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04061781987547874</v>
+        <v>0.7466132044792175</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009414858650416136</v>
+        <v>0.3070592880249023</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01145084761083126</v>
+        <v>0.8237820863723755</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0173882357776165</v>
+        <v>0.5321812629699707</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001351742073893547</v>
+        <v>0.2842823266983032</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004573669284582138</v>
+        <v>0.4423660933971405</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005372557323426008</v>
+        <v>0.229914978146553</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007503869477659464</v>
+        <v>0.1792155802249908</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002422972116619349</v>
+        <v>0.0279361866414547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004105490166693926</v>
+        <v>0.2189404964447021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004410544410347939</v>
+        <v>0.1711119413375854</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003437021048739552</v>
+        <v>0.1497301608324051</v>
       </c>
       <c r="W5" t="n">
-        <v>0.009588848799467087</v>
+        <v>0.01628143340349197</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004664668813347816</v>
+        <v>0.03032154217362404</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003279224038124084</v>
+        <v>0.04750630259513855</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004286324139684439</v>
+        <v>0.06662063300609589</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001081835944205523</v>
+        <v>0.1172191277146339</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.005659165326505899</v>
+        <v>0.1189171150326729</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005163409281522036</v>
+        <v>0.001406220719218254</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.007746493443846703</v>
+        <v>0.1708227545022964</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.002622566651552916</v>
+        <v>0.01074985042214394</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.006642768159508705</v>
+        <v>0.2465305924415588</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003643987933173776</v>
+        <v>0.2310446053743362</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001485739951021969</v>
+        <v>0.1051336675882339</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.008663799613714218</v>
+        <v>0.03939812257885933</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.005689719691872597</v>
+        <v>0.08900956064462662</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.007740095723420382</v>
+        <v>0.01212592795491219</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.00660631712526083</v>
+        <v>0.37958163022995</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.005512486211955547</v>
+        <v>0.0838019996881485</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.006229295395314693</v>
+        <v>0.2018845677375793</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.006332383025437593</v>
+        <v>0.474824845790863</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.007358799688518047</v>
+        <v>0.09940263628959656</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.003839748213067651</v>
+        <v>0.265818327665329</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.007366835605353117</v>
+        <v>0.3103933930397034</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.000957460782956332</v>
+        <v>0.05699150264263153</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001713092089630663</v>
+        <v>0.006619162857532501</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.02337165549397469</v>
+        <v>0.7456692457199097</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003640915500000119</v>
+        <v>0.04563988745212555</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.01738225109875202</v>
+        <v>0.4339510202407837</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.03028793819248676</v>
+        <v>0.08692235499620438</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.01450343523174524</v>
+        <v>0.2161065489053726</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01086445711553097</v>
+        <v>0.1665544211864471</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0172124095261097</v>
+        <v>0.04044060781598091</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001064001116901636</v>
+        <v>0.2671117782592773</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.007663638330996037</v>
+        <v>0.05097648501396179</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00849311426281929</v>
+        <v>0.4614637494087219</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003151040058583021</v>
+        <v>0.3126752078533173</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.001872660242952406</v>
+        <v>0.1429885029792786</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001498052850365639</v>
+        <v>0.478787750005722</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01016920153051615</v>
+        <v>0.1938920319080353</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001012688037008047</v>
+        <v>0.4388026297092438</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.008827216923236847</v>
+        <v>0.2783251404762268</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.01350681856274605</v>
+        <v>0.2889645099639893</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0106610432267189</v>
+        <v>0.03604063391685486</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.004275843501091003</v>
+        <v>0.08919361233711243</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.008371321484446526</v>
+        <v>0.08222163468599319</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01675086468458176</v>
+        <v>0.1012558043003082</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.004734055604785681</v>
+        <v>0.2236463278532028</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0001759715378284454</v>
+        <v>0.07907950878143311</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001828819047659636</v>
+        <v>0.008418276906013489</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.002800753805786371</v>
+        <v>0.1996175944805145</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.005098513327538967</v>
+        <v>0.121270164847374</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.007649848703294992</v>
+        <v>0.008186781778931618</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02074018493294716</v>
+        <v>0.833915114402771</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.002025779336690903</v>
+        <v>0.1018662974238396</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01631029509007931</v>
+        <v>0.590132474899292</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01637838780879974</v>
+        <v>0.1283733248710632</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001447863411158323</v>
+        <v>0.08778543770313263</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002280161716043949</v>
+        <v>0.01379742473363876</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.005086856428533792</v>
+        <v>0.03308840095996857</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001180661842226982</v>
+        <v>0.1139580011367798</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.002684720559045672</v>
+        <v>0.0008017374202609062</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.002520229201763868</v>
+        <v>0.3277750909328461</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0007683181902393699</v>
+        <v>0.08912234008312225</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.001059911912307143</v>
+        <v>0.2577597200870514</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.003842648817226291</v>
+        <v>0.04130489006638527</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.002685466082766652</v>
+        <v>0.00767749547958374</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0009998839814215899</v>
+        <v>0.0270347073674202</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001072644721716642</v>
+        <v>0.1115610748529434</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001846327679231763</v>
+        <v>0.0602111779153347</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.008302508853375912</v>
+        <v>0.03468023985624313</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.006836431566625834</v>
+        <v>0.451537013053894</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.004955760203301907</v>
+        <v>0.04802246019244194</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.01066792849451303</v>
+        <v>0.5285167694091797</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002265059854835272</v>
+        <v>0.3374284505844116</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.01111826114356518</v>
+        <v>0.108872726559639</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.01234683580696583</v>
+        <v>0.1182809844613075</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002031429903581738</v>
+        <v>0.3050305843353271</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002520925365388393</v>
+        <v>0.1211739778518677</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0004531653830781579</v>
+        <v>0.02700070850551128</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.005228113848716021</v>
+        <v>0.3237895965576172</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0002628255169838667</v>
+        <v>0.1062943115830421</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0009385384037159383</v>
+        <v>0.2722501456737518</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.007062072865664959</v>
+        <v>0.007951064966619015</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.005118939559906721</v>
+        <v>0.008464782498776913</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003782367566600442</v>
+        <v>0.01048388332128525</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.002376215998083353</v>
+        <v>0.07786452770233154</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001197567326016724</v>
+        <v>0.1018457859754562</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.003500722348690033</v>
+        <v>0.05309178307652473</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01440755091607571</v>
+        <v>0.4883487522602081</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00426251906901598</v>
+        <v>0.2607312500476837</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.006451386958360672</v>
+        <v>0.3501526713371277</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002781233517453074</v>
+        <v>0.3219150304794312</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004583647008985281</v>
+        <v>0.3588755428791046</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.005583569407463074</v>
+        <v>0.06924286484718323</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.009972834959626198</v>
+        <v>0.4208618700504303</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0003464699257165194</v>
+        <v>0.1419453024864197</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.003193981712684035</v>
+        <v>0.0503845177590847</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.01267795357853174</v>
+        <v>0.09405519813299179</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.01323436759412289</v>
+        <v>0.116843044757843</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01151656359434128</v>
+        <v>0.04716899618506432</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.004522019997239113</v>
+        <v>0.04823603108525276</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.01140048541128635</v>
+        <v>0.03690634667873383</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.002276596380397677</v>
+        <v>0.0008316803723573685</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0005199764855206013</v>
+        <v>0.1516564190387726</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.006188212893903255</v>
+        <v>0.5696437358856201</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001304875244386494</v>
+        <v>0.0461035780608654</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.002981320954859257</v>
+        <v>0.06250821053981781</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.003103039460256696</v>
+        <v>0.1945846080780029</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.004116601776331663</v>
+        <v>0.02271455526351929</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01183981541544199</v>
+        <v>0.3209937512874603</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001880671130493283</v>
+        <v>0.1978480368852615</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0002985442406497896</v>
+        <v>0.09834904223680496</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001680364250205457</v>
+        <v>0.3435876965522766</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.001099892891943455</v>
+        <v>0.4872441291809082</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001503314473666251</v>
+        <v>0.04401640966534615</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001476570381782949</v>
+        <v>0.3358166813850403</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.003263507271185517</v>
+        <v>0.1420346945524216</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.004548790398985147</v>
+        <v>0.2703774571418762</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001955967396497726</v>
+        <v>0.1156970113515854</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01187621988356113</v>
+        <v>0.003110694698989391</v>
       </c>
       <c r="EL5" t="n">
-        <v>2.760114148259163e-05</v>
+        <v>0.0500163733959198</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001520815421827137</v>
+        <v>0.0114478338509798</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0006218015914782882</v>
+        <v>0.02043081820011139</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.002065693028271198</v>
+        <v>0.02446159906685352</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.003146421862766147</v>
+        <v>0.2744402289390564</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.005703654140233994</v>
+        <v>0.1135680451989174</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.001400515204295516</v>
+        <v>0.2695388793945312</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.009317701682448387</v>
+        <v>0.1465303152799606</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.02045193500816822</v>
+        <v>0.08360929787158966</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.007248984649777412</v>
+        <v>0.03154660388827324</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.01093590911477804</v>
+        <v>0.1640809774398804</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.003482030471786857</v>
+        <v>0.007561761885881424</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001250039436854422</v>
+        <v>0.001476324163377285</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003123471280559897</v>
+        <v>0.3957089483737946</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001483140280470252</v>
+        <v>0.07172574102878571</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001898232148960233</v>
+        <v>0.3289660811424255</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.003245552070438862</v>
+        <v>0.0296382699161768</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.004162751603871584</v>
+        <v>0.0505809560418129</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.002576461993157864</v>
+        <v>0.005153771489858627</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.000665988540276885</v>
+        <v>0.1005065590143204</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0006412486545741558</v>
+        <v>0.07318878173828125</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.002670965623110533</v>
+        <v>0.05548457056283951</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.003520167898386717</v>
+        <v>0.2517989277839661</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.008503441698849201</v>
+        <v>0.1483675539493561</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.003961936570703983</v>
+        <v>0.1782061010599136</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01009442936629057</v>
+        <v>0.02815001644194126</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.009506842121481895</v>
+        <v>0.01135005801916122</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004568473435938358</v>
+        <v>0.01184831187129021</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0004722191952168941</v>
+        <v>0.155869260430336</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.002750318730250001</v>
+        <v>0.3730612099170685</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.007115249987691641</v>
+        <v>0.04458630084991455</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0204017236828804</v>
+        <v>0.3167297840118408</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001251050271093845</v>
+        <v>0.1323661953210831</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0195614080876112</v>
+        <v>0.2802335619926453</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01441361755132675</v>
+        <v>0.3069762587547302</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.007124067284166813</v>
+        <v>0.06503322720527649</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.01113823801279068</v>
+        <v>0.1423729062080383</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.005282262340188026</v>
+        <v>0.1734733134508133</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.008350256830453873</v>
+        <v>0.1342553347349167</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0004471386782824993</v>
+        <v>0.06204153597354889</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.003637646557763219</v>
+        <v>0.3083732128143311</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0001173483906313777</v>
+        <v>0.005549661815166473</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.007200871594250202</v>
+        <v>0.2524853050708771</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.01513841934502125</v>
+        <v>0.209026500582695</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0005992957740090787</v>
+        <v>0.1967571675777435</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.009363690391182899</v>
+        <v>0.06740550696849823</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.009927686303853989</v>
+        <v>0.06477926671504974</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0006716297939419746</v>
+        <v>0.03961991891264915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.03739335760474205</v>
+        <v>0.01153800077736378</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2699053883552551</v>
+        <v>0.09889291971921921</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0226933341473341</v>
+        <v>0.02746056392788887</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1341632306575775</v>
+        <v>0.07372881472110748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06383249908685684</v>
+        <v>0.004676101263612509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00374957243911922</v>
+        <v>0.04842930287122726</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001608948921784759</v>
+        <v>0.04249381646513939</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03185800090432167</v>
+        <v>0.02588463202118874</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02107728645205498</v>
+        <v>0.004949262831360102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002915218472480774</v>
+        <v>0.01659774221479893</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2317856997251511</v>
+        <v>0.09885738790035248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007817814126610756</v>
+        <v>0.0347529873251915</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1442780494689941</v>
+        <v>0.1127876341342926</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1063307002186775</v>
+        <v>0.03545548394322395</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0191972553730011</v>
+        <v>0.03564377129077911</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01713139750063419</v>
+        <v>0.04572129994630814</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05548355728387833</v>
+        <v>0.008417638950049877</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01335503347218037</v>
+        <v>0.006996187381446362</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02904696390032768</v>
+        <v>0.000459783710539341</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0292273722589016</v>
+        <v>0.003842270001769066</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03904701396822929</v>
+        <v>0.001069260761141777</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02420481480658054</v>
+        <v>0.01048202067613602</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04170496761798859</v>
+        <v>0.01134217996150255</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04271496087312698</v>
+        <v>0.02667408622801304</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03512229770421982</v>
+        <v>0.005704863928258419</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0171828381717205</v>
+        <v>0.006241107359528542</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01693186908960342</v>
+        <v>0.01702056638896465</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04324797540903091</v>
+        <v>0.01073486264795065</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07255533337593079</v>
+        <v>0.01562980003654957</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0249812975525856</v>
+        <v>0.02339374274015427</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001640852075070143</v>
+        <v>0.0005371121224015951</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0070030577480793</v>
+        <v>0.00968674011528492</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02338666468858719</v>
+        <v>0.03591322898864746</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.002412555739283562</v>
+        <v>0.0179637148976326</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02444207295775414</v>
+        <v>0.01271224580705166</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.000859494786709547</v>
+        <v>0.01041853148490191</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01137528102844954</v>
+        <v>0.0003203651867806911</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005373027175664902</v>
+        <v>0.04035140946507454</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.01558470726013184</v>
+        <v>0.01878283731639385</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.004677766934037209</v>
+        <v>0.01259743236005306</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.03686335682868958</v>
+        <v>0.01178002916276455</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.02859924733638763</v>
+        <v>0.01689513958990574</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.02374360710382462</v>
+        <v>0.0146192517131567</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.005920925177633762</v>
+        <v>0.0008388739079236984</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.009175547398626804</v>
+        <v>0.005588099360466003</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.006585287861526012</v>
+        <v>0.01539844740182161</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1963585615158081</v>
+        <v>0.04652801156044006</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.03618905693292618</v>
+        <v>0.01900806650519371</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.07186870276927948</v>
+        <v>0.02942298725247383</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.005177953746169806</v>
+        <v>0.06898649036884308</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01951982639729977</v>
+        <v>0.02248302660882473</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.03682732209563255</v>
+        <v>0.01120705995708704</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.06606008857488632</v>
+        <v>0.00169875321444124</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.03903220966458321</v>
+        <v>0.02266378328204155</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.05615414679050446</v>
+        <v>0.012850072234869</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.07816268503665924</v>
+        <v>0.003517249831929803</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07433780282735825</v>
+        <v>0.03639839589595795</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.02291721850633621</v>
+        <v>0.0002174489200115204</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.03325532749295235</v>
+        <v>0.02076221629977226</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.06172941625118256</v>
+        <v>0.02123373188078403</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03389301151037216</v>
+        <v>0.02501347661018372</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.004035657271742821</v>
+        <v>0.0007163363043218851</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.003039813600480556</v>
+        <v>0.02152246236801147</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.06414052844047546</v>
+        <v>0.001193921198137105</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04391572251915932</v>
+        <v>0.001779283746145666</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.03938494250178337</v>
+        <v>0.003247338347136974</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02218742109835148</v>
+        <v>0.01186588499695063</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.05838710069656372</v>
+        <v>0.01050702389329672</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.02304988726973534</v>
+        <v>0.001431602519005537</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0472339391708374</v>
+        <v>0.001362066017463803</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.005519561469554901</v>
+        <v>0.009771391749382019</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.004677197895944118</v>
+        <v>0.0001046680117724463</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.02013921365141869</v>
+        <v>0.004728803411126137</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0958559513092041</v>
+        <v>0.04152641817927361</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.02572966739535332</v>
+        <v>0.006801562383770943</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0133372126147151</v>
+        <v>0.05068573355674744</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.04406241327524185</v>
+        <v>0.01677479594945908</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.05854186043143272</v>
+        <v>0.02310457080602646</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.008055167272686958</v>
+        <v>0.01056038495153189</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.03130717575550079</v>
+        <v>0.0004231795901432633</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0226663202047348</v>
+        <v>0.01311594806611538</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.003373432904481888</v>
+        <v>0.004376498982310295</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.03816709294915199</v>
+        <v>0.03720737621188164</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.001087659038603306</v>
+        <v>0.001397286541759968</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01498901285231113</v>
+        <v>0.03081072494387627</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0001346633653156459</v>
+        <v>0.0008109244517982006</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.004192755091935396</v>
+        <v>0.01345508545637131</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.003785870037972927</v>
+        <v>0.0009371287887915969</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0003243410028517246</v>
+        <v>0.008471217006444931</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0125734880566597</v>
+        <v>0.001385691692121327</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.05212254822254181</v>
+        <v>0.01909738034009933</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.05841996520757675</v>
+        <v>0.01795259863138199</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01527481526136398</v>
+        <v>0.04284194484353065</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.02463505789637566</v>
+        <v>0.06521229445934296</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0757296234369278</v>
+        <v>0.03115726448595524</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.00576789490878582</v>
+        <v>0.02215112186968327</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.01031570043414831</v>
+        <v>0.01180156227201223</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.05734725669026375</v>
+        <v>0.002839030930772424</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.01311134919524193</v>
+        <v>0.007003117818385363</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.007050676736980677</v>
+        <v>0.004149007610976696</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.03620037063956261</v>
+        <v>0.03541095927357674</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01611388102173805</v>
+        <v>0.005465594120323658</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01874595880508423</v>
+        <v>0.03246821463108063</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001449470175430179</v>
+        <v>0.005718284286558628</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.002572877798229456</v>
+        <v>0.0138128874823451</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.004265828058123589</v>
+        <v>0.002764926990494132</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.01099217589944601</v>
+        <v>0.006743358448147774</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.01091180276125669</v>
+        <v>0.004105379804968834</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06017819046974182</v>
+        <v>0.004388311877846718</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.01964991539716721</v>
+        <v>0.00977388396859169</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.03306761011481285</v>
+        <v>0.003549293614923954</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1482735723257065</v>
+        <v>0.02180932275950909</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05334562435746193</v>
+        <v>0.02443488501012325</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.03982315957546234</v>
+        <v>0.05910236015915871</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.002729838714003563</v>
+        <v>0.0006759399548172951</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.03377054631710052</v>
+        <v>0.04486867785453796</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.003731064032763243</v>
+        <v>0.005497288890182972</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0069866175763309</v>
+        <v>0.006081458181142807</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0120445815846324</v>
+        <v>0.02590359747409821</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.02036822773516178</v>
+        <v>0.002467579208314419</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.03741003945469856</v>
+        <v>0.01858571916818619</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03144824877381325</v>
+        <v>0.002775394357740879</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.01585610397160053</v>
+        <v>0.0003444284666329622</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01341837365180254</v>
+        <v>0.009076260030269623</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.006315264385193586</v>
+        <v>0.01800558902323246</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.01430458016693592</v>
+        <v>0.03022138401865959</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.02335991337895393</v>
+        <v>0.004387565888464451</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.08018127828836441</v>
+        <v>0.009098483249545097</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.03390006348490715</v>
+        <v>0.02808628603816032</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.04556626081466675</v>
+        <v>0.01460377220064402</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.03749961033463478</v>
+        <v>0.01136311143636703</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.05383412912487984</v>
+        <v>0.0214436911046505</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.01100247912108898</v>
+        <v>0.0007435439620167017</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.007617129012942314</v>
+        <v>0.04598566889762878</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.002155407099053264</v>
+        <v>0.0441247746348381</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.02182621695101261</v>
+        <v>0.01841822452843189</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01978726498782635</v>
+        <v>0.01765666157007217</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.001862486591562629</v>
+        <v>0.02270299941301346</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.03583057969808578</v>
+        <v>0.03000219911336899</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.05469483882188797</v>
+        <v>0.004985082894563675</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02610488422214985</v>
+        <v>0.01123518962413073</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.002312755212187767</v>
+        <v>0.0005126697942614555</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.009766311384737492</v>
+        <v>0.002519649919122458</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01523220632225275</v>
+        <v>9.119650349020958e-05</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.009277178905904293</v>
+        <v>0.005969510413706303</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.03935408964753151</v>
+        <v>0.04193822294473648</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01116442028433084</v>
+        <v>0.01129801198840141</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.001968850381672382</v>
+        <v>0.02741210348904133</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.009736549109220505</v>
+        <v>0.01686830632388592</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.04861209541559219</v>
+        <v>0.001116745173931122</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.03167795762419701</v>
+        <v>0.009354948997497559</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.02325346693396568</v>
+        <v>0.01528334245085716</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0003434000536799431</v>
+        <v>0.01290507242083549</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.009830097667872906</v>
+        <v>0.001955909887328744</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.03705548495054245</v>
+        <v>0.0400334820151329</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001731670461595058</v>
+        <v>0.001830545719712973</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.014711057767272</v>
+        <v>0.03727949783205986</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01737057790160179</v>
+        <v>0.004819779191166162</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01332392264157534</v>
+        <v>0.01626507379114628</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.009897897019982338</v>
+        <v>0.004349172115325928</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.008658880367875099</v>
+        <v>0.0119321383535862</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.01402711775153875</v>
+        <v>0.007428450975567102</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.000245245813857764</v>
+        <v>0.005653382744640112</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.05500026047229767</v>
+        <v>0.00348671292886138</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.03148240596055984</v>
+        <v>0.00390871474519372</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.007552764844149351</v>
+        <v>0.006901030894368887</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.02947556972503662</v>
+        <v>0.02868625894188881</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01140993926674128</v>
+        <v>0.01480007637292147</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.04638155549764633</v>
+        <v>0.0002493252977728844</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.01973504200577736</v>
+        <v>0.006945809815078974</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.002449026331305504</v>
+        <v>0.003962617833167315</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.03325269371271133</v>
+        <v>0.01259702257812023</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.07451040297746658</v>
+        <v>0.01783390715718269</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.006737147457897663</v>
+        <v>0.02273685857653618</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.04017270356416702</v>
+        <v>0.0174073651432991</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.07214812934398651</v>
+        <v>0.03423909097909927</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.04737302660942078</v>
+        <v>0.02146436646580696</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.02110054902732372</v>
+        <v>0.002492544241249561</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.01825692132115364</v>
+        <v>0.02199598215520382</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01022947020828724</v>
+        <v>0.02888270653784275</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.01001286134123802</v>
+        <v>0.006964558735489845</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.03881563618779182</v>
+        <v>0.009367499500513077</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0192609503865242</v>
+        <v>0.001356807770207524</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.03351539745926857</v>
+        <v>0.04618454724550247</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.00090817641466856</v>
+        <v>0.01806400902569294</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.06213067471981049</v>
+        <v>0.01671070978045464</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.02621090784668922</v>
+        <v>0.02276382222771645</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.01169221848249435</v>
+        <v>0.01128974463790655</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.008877632208168507</v>
+        <v>0.01174833718687296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01859480701386929</v>
+        <v>0.01548852492123842</v>
       </c>
       <c r="B7" t="n">
-        <v>0.003786544781178236</v>
+        <v>0.008649836294353008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005217570811510086</v>
+        <v>0.01867731101810932</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006719207391142845</v>
+        <v>0.07821646332740784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004000456072390079</v>
+        <v>0.01470415387302637</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004997101612389088</v>
+        <v>0.008417867124080658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002082758117467165</v>
+        <v>0.02313192188739777</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001485139015130699</v>
+        <v>0.008323404006659985</v>
       </c>
       <c r="I7" t="n">
-        <v>7.373886182904243e-05</v>
+        <v>0.00814861711114645</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01678964681923389</v>
+        <v>0.01517616771161556</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008411011658608913</v>
+        <v>0.00577928964048624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00594295421615243</v>
+        <v>0.01788468100130558</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002914434298872948</v>
+        <v>0.1015104353427887</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004480548202991486</v>
+        <v>0.001423167530447245</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000225235620746389</v>
+        <v>0.0278964601457119</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001522232545539737</v>
+        <v>0.02791798673570156</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001410093740560114</v>
+        <v>0.009317561984062195</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001010480802506208</v>
+        <v>0.005783070810139179</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001776799792423844</v>
+        <v>0.001801895210519433</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003484271001070738</v>
+        <v>0.001358206383883953</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001788571011275053</v>
+        <v>0.001898808754049242</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002643991902004927</v>
+        <v>0.009008648805320263</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002770509105175734</v>
+        <v>0.008580995723605156</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0009206131799146533</v>
+        <v>0.01509321201592684</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004132854810450226</v>
+        <v>0.002072907984256744</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002246114425361156</v>
+        <v>0.003146637696772814</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001099793371395208</v>
+        <v>0.003028673585504293</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001780954422429204</v>
+        <v>0.009843043982982635</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003577170195057988</v>
+        <v>0.007683882489800453</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001969604985788465</v>
+        <v>0.001833578571677208</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002526284195482731</v>
+        <v>0.003061551367864013</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001786258537322283</v>
+        <v>0.007606750354170799</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0007564446423202753</v>
+        <v>0.0113093750551343</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0007663870928809047</v>
+        <v>0.006693350151181221</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002202934585511684</v>
+        <v>0.009306492283940315</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001524775754660368</v>
+        <v>0.01325064059346914</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.002869895193725824</v>
+        <v>0.004280040506273508</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0006699452642351389</v>
+        <v>0.01115547399967909</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001167363254353404</v>
+        <v>2.22580274567008e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002031943993642926</v>
+        <v>0.01487956568598747</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003200612030923367</v>
+        <v>0.00120056455489248</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001717783743515611</v>
+        <v>0.005349679850041866</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001406849245540798</v>
+        <v>0.01373682543635368</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.002824324415996671</v>
+        <v>0.001465019769966602</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001063693314790726</v>
+        <v>0.001156760030426085</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01145944837480783</v>
+        <v>0.001969237811863422</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.004371169488877058</v>
+        <v>0.005131260491907597</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.006561951246112585</v>
+        <v>0.000752056366764009</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.004429676569998264</v>
+        <v>0.04841573163866997</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.00501065980643034</v>
+        <v>0.02963836304843426</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.002302903216332197</v>
+        <v>0.005947571247816086</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001371437916532159</v>
+        <v>0.002454270608723164</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002981709083542228</v>
+        <v>0.009878772310912609</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001964873401448131</v>
+        <v>0.003589356318116188</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.007419855333864689</v>
+        <v>0.01520735304802656</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.009217415004968643</v>
+        <v>0.004263491835445166</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0003175009042024612</v>
+        <v>0.006910729221999645</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001314257038757205</v>
+        <v>0.01096135657280684</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.004424002952873707</v>
+        <v>0.01718353666365147</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001683313632383943</v>
+        <v>0.0001928540877997875</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.001379526569508016</v>
+        <v>0.0112990103662014</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.004267353098839521</v>
+        <v>0.01123622059822083</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.003734847996383905</v>
+        <v>0.02205985225737095</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0004349427472334355</v>
+        <v>0.005789997987449169</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.003950595390051603</v>
+        <v>0.004343193955719471</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.000901879626326263</v>
+        <v>0.00507722981274128</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001337006455287337</v>
+        <v>0.009046283550560474</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.000697410898283124</v>
+        <v>0.01643356494605541</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.001578093273565173</v>
+        <v>0.00493921060115099</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001697345869615674</v>
+        <v>0.003632384119555354</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001904424745589495</v>
+        <v>0.003591398242861032</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.00107720703817904</v>
+        <v>0.0044067008420825</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.004506704863160849</v>
+        <v>0.001363047864288092</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0005398414214141667</v>
+        <v>0.001445623696781695</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.00223671505227685</v>
+        <v>0.002245450392365456</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.001141536980867386</v>
+        <v>0.04069651290774345</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004442537028808147</v>
+        <v>0.01349428109824657</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0004402635095175356</v>
+        <v>0.01250529941171408</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001221571583300829</v>
+        <v>0.002203206997364759</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002340778475627303</v>
+        <v>9.342710836790502e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001705627655610442</v>
+        <v>0.006469273939728737</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.00375156057998538</v>
+        <v>0.004911236464977264</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001994071993976831</v>
+        <v>0.006944288033992052</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002975031093228608</v>
+        <v>0.0005444338312372565</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0001421068009221926</v>
+        <v>0.02624239400029182</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.175302819930948e-05</v>
+        <v>6.49293651804328e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.002509454032406211</v>
+        <v>0.006688749417662621</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0002228505909442902</v>
+        <v>0.001058825524523854</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001864401157945395</v>
+        <v>0.007800277322530746</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0002547103213146329</v>
+        <v>0.003153161611407995</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.00431936327368021</v>
+        <v>0.0008399698417633772</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003446283983066678</v>
+        <v>0.008781731128692627</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0004850420518778265</v>
+        <v>0.01524677779525518</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.003038925118744373</v>
+        <v>0.03775549307465553</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.005414618644863367</v>
+        <v>0.02113156951963902</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0007916099275462329</v>
+        <v>0.011377127841115</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.003270076122134924</v>
+        <v>4.275143146514893e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.004789199680089951</v>
+        <v>0.01310723926872015</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001165695837698877</v>
+        <v>0.0132405636832118</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.003235361771658063</v>
+        <v>0.003860944183543324</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.002170246094465256</v>
+        <v>0.006936279125511646</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0005784877575933933</v>
+        <v>0.001098777167499065</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0004950099973939359</v>
+        <v>0.02863804064691067</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0006381505518220365</v>
+        <v>0.001865458558313549</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002224367344751954</v>
+        <v>0.002335535362362862</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0004933223826810718</v>
+        <v>0.003589792642742395</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001293498440645635</v>
+        <v>0.006677405908703804</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001610836770851165</v>
+        <v>0.001415936509147286</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0007240416016429663</v>
+        <v>3.972905687987804e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.005172550678253174</v>
+        <v>0.01394752319902182</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.005782011896371841</v>
+        <v>0.002721943892538548</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.00719918729737401</v>
+        <v>0.01388890948146582</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.004943049978464842</v>
+        <v>0.002424174686893821</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001885124598629773</v>
+        <v>0.01567305251955986</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0002197102876380086</v>
+        <v>0.004435768350958824</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.006407205015420914</v>
+        <v>0.02727821655571461</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.00216430751606822</v>
+        <v>0.0007184320129454136</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.002084808424115181</v>
+        <v>0.00167689030058682</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0004916624748148024</v>
+        <v>0.009467475116252899</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.00145042478106916</v>
+        <v>0.01532376930117607</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.002091817790642381</v>
+        <v>0.009549839422106743</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.004232440143823624</v>
+        <v>0.008936897851526737</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.001558443647809327</v>
+        <v>0.00370749831199646</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.001615514396689832</v>
+        <v>0.007579241879284382</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0007664142758585513</v>
+        <v>0.003523984923958778</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.002226756885647774</v>
+        <v>0.01742017827928066</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.002404116792604327</v>
+        <v>0.0007969242287799716</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.001348817255347967</v>
+        <v>0.002817812375724316</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0005616003763861954</v>
+        <v>0.03234321624040604</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0006591855199076235</v>
+        <v>0.007790635339915752</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.00121899601072073</v>
+        <v>0.0001984465634450316</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0008926121518015862</v>
+        <v>0.01035505346953869</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004011275013908744</v>
+        <v>0.004644794855266809</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0003936152788810432</v>
+        <v>0.02650767751038074</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.00118774245493114</v>
+        <v>0.017327930778265</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.004075716715306044</v>
+        <v>0.01733851246535778</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.003714392427355051</v>
+        <v>0.002045059576630592</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.002780669601634145</v>
+        <v>0.001034364802762866</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.003256602911278605</v>
+        <v>0.02676131948828697</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004552324768155813</v>
+        <v>0.003008917206898332</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0007877607713453472</v>
+        <v>0.007678132969886065</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0004277898115105927</v>
+        <v>0.002631014678627253</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0004130964516662061</v>
+        <v>0.003506573149934411</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0003383022558409721</v>
+        <v>0.0001004610676318407</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0006456417613662779</v>
+        <v>0.005497912876307964</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.004789563827216625</v>
+        <v>0.009639066644012928</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001769191352650523</v>
+        <v>0.007986413314938545</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0004965122207067907</v>
+        <v>0.0235818512737751</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.001898746006190777</v>
+        <v>0.002325982321053743</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.003516346216201782</v>
+        <v>0.01289281435310841</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.001471554976888001</v>
+        <v>0.01001233235001564</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.001811930793337524</v>
+        <v>0.0091443145647645</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.003192866686731577</v>
+        <v>0.01216932572424412</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.003121481742709875</v>
+        <v>0.003560690674930811</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.002462099306285381</v>
+        <v>0.004315780010074377</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001181157538667321</v>
+        <v>0.001862148521468043</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0005999491550028324</v>
+        <v>0.0313798189163208</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0004912898875772953</v>
+        <v>0.000201490125618875</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.002309436909854412</v>
+        <v>0.001821715850383043</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0004923711530864239</v>
+        <v>0.003479202976450324</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001510529546067119</v>
+        <v>0.009215482510626316</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0004031471617054194</v>
+        <v>0.001504243118688464</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.000267689349129796</v>
+        <v>4.798127338290215e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.004114364273846149</v>
+        <v>0.002042778301984072</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.004789531696587801</v>
+        <v>0.007038717158138752</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.001150155789218843</v>
+        <v>0.01460119057446718</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001398969907313585</v>
+        <v>0.01352878101170063</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.00422277906909585</v>
+        <v>0.006315577775239944</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0008805707329884171</v>
+        <v>0.003719697706401348</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0002611310046631843</v>
+        <v>0.0101780267432332</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.001131762517616153</v>
+        <v>0.004843039438128471</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.002696168376132846</v>
+        <v>0.01531954295933247</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.001648248871788383</v>
+        <v>0.0240336749702692</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.002666207030415535</v>
+        <v>0.002421772573143244</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.003158370032906532</v>
+        <v>0.02976083755493164</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.002712693065404892</v>
+        <v>0.006765523925423622</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.005217984784394503</v>
+        <v>0.02862241491675377</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.001129085896536708</v>
+        <v>0.003858401672914624</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0009767822921276093</v>
+        <v>0.01846292801201344</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0003225830150768161</v>
+        <v>0.007585932034999132</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.001056641340255737</v>
+        <v>0.004597955383360386</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.000384196697268635</v>
+        <v>0.001116893254220486</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0001599593670107424</v>
+        <v>0.006133710965514183</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001085432129912078</v>
+        <v>0.02733239158987999</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.004707451909780502</v>
+        <v>0.007262325845658779</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0001074284955393523</v>
+        <v>0.009871276095509529</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001805152278393507</v>
+        <v>0.02000761218369007</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0007592682959511876</v>
+        <v>0.007570024114102125</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001295808237046003</v>
+        <v>0.001413475023582578</v>
       </c>
     </row>
     <row r="8">
@@ -5551,2847 +5551,2847 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0001468381815357134</v>
+        <v>2.957670197645257e-08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0007903942605480552</v>
+        <v>9.931915201377706e-08</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001065293545252644</v>
+        <v>7.269354007632955e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005460709217004478</v>
+        <v>6.836441457380715e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002536386891733855</v>
+        <v>2.188880365849855e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001895679160952568</v>
+        <v>5.940357539202523e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>6.823975854786113e-05</v>
+        <v>1.835270424521696e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>9.908771971822716e-06</v>
+        <v>2.760756245834273e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>4.71417952212505e-05</v>
+        <v>9.062333661269406e-10</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002235939318779856</v>
+        <v>1.552684869565724e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0006156442104838789</v>
+        <v>9.524910637992434e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>8.898686792235821e-05</v>
+        <v>7.563130566268228e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003891409724019468</v>
+        <v>1.0452511389758e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0003192287113051862</v>
+        <v>5.649264167573165e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003708633303176612</v>
+        <v>5.197962593683769e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>9.186423994833604e-05</v>
+        <v>1.014290784695504e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001731761876726523</v>
+        <v>1.057337950527426e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>8.49757925607264e-05</v>
+        <v>1.210771372051056e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>2.492488420102745e-07</v>
+        <v>8.166259668485054e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0001378296437906101</v>
+        <v>9.344915063991266e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>4.54977634944953e-05</v>
+        <v>2.926460496155414e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>7.326799095608294e-05</v>
+        <v>8.536802376113428e-10</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001218931211042218</v>
+        <v>1.973276653188805e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0001103805843740702</v>
+        <v>1.59655861864394e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.000142773860716261</v>
+        <v>2.9552330360616e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.437274376163259e-05</v>
+        <v>2.068498794471907e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0001282720186281949</v>
+        <v>6.878386749065157e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.30733198300004e-05</v>
+        <v>1.211809319556778e-09</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.246732224710286e-05</v>
+        <v>1.667112492498291e-08</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.578224616125226e-05</v>
+        <v>1.042913133630918e-08</v>
       </c>
       <c r="AE10" t="n">
-        <v>6.518064765259624e-05</v>
+        <v>2.866140569324216e-08</v>
       </c>
       <c r="AF10" t="n">
-        <v>6.302418478298932e-05</v>
+        <v>1.391452553178851e-08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.532714486529585e-05</v>
+        <v>3.420260696884725e-08</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.67138519929722e-05</v>
+        <v>7.868102613883821e-09</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.592402259120718e-05</v>
+        <v>3.629228828572195e-08</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.024827598594129e-06</v>
+        <v>6.908948968487039e-09</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0001006445309030823</v>
+        <v>1.024652984682461e-08</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.98167787049897e-05</v>
+        <v>1.70099063723228e-08</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.151451139478013e-05</v>
+        <v>4.00609607709157e-08</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.85171952075325e-05</v>
+        <v>2.823629507986425e-08</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.348364018369466e-05</v>
+        <v>1.502512247952836e-08</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.06790955417091e-05</v>
+        <v>2.32719976622775e-08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.325239908415824e-05</v>
+        <v>4.998854219451232e-09</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.97277256322559e-05</v>
+        <v>3.016898064700513e-09</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.975175347179174e-05</v>
+        <v>7.602186435917702e-09</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.190288043697365e-05</v>
+        <v>5.593284946314725e-09</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0005182874738238752</v>
+        <v>7.167096782723092e-08</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.318683593533933e-05</v>
+        <v>5.409477310536204e-08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0001086972843040712</v>
+        <v>1.792324511029619e-09</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.517651591915637e-05</v>
+        <v>8.990690503196674e-08</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.960476922453381e-05</v>
+        <v>5.822538184929726e-08</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.899540438898839e-05</v>
+        <v>1.673468474905349e-09</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0001345861237496138</v>
+        <v>1.203802657556707e-08</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.324422378791496e-05</v>
+        <v>4.541598652707535e-09</v>
       </c>
       <c r="BC10" t="n">
-        <v>9.176424646284431e-05</v>
+        <v>1.117390624472137e-08</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.477068331558257e-05</v>
+        <v>3.105152757143514e-08</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0002420684177195653</v>
+        <v>1.493611456737653e-08</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0001121997120208107</v>
+        <v>3.757292788009181e-08</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.000274941063253209</v>
+        <v>5.988594153905069e-08</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0001222759892698377</v>
+        <v>9.114457633074835e-09</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.196077366534155e-05</v>
+        <v>4.902855899047154e-09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0001702118752291426</v>
+        <v>3.050499230994319e-08</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.758694245130755e-05</v>
+        <v>9.555152225004804e-09</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0001271166693186387</v>
+        <v>5.411584957926152e-09</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0001300677104154602</v>
+        <v>1.631910251376212e-08</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0001003815996227786</v>
+        <v>2.520208486345155e-09</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.151228106115013e-05</v>
+        <v>1.747535804952349e-08</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0001327045611105859</v>
+        <v>3.353940059014349e-08</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.432753823697567e-05</v>
+        <v>2.055428938163573e-09</v>
       </c>
       <c r="BR10" t="n">
-        <v>3.789693437283859e-05</v>
+        <v>8.758807901187993e-09</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0001210915070259944</v>
+        <v>9.979293835726821e-09</v>
       </c>
       <c r="BT10" t="n">
-        <v>3.344694050610997e-06</v>
+        <v>3.591943409375631e-09</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.67962716659531e-05</v>
+        <v>1.753838851925593e-09</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0002318589831702411</v>
+        <v>3.999831221790373e-08</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0001267824700335041</v>
+        <v>2.937432519445338e-08</v>
       </c>
       <c r="BX10" t="n">
-        <v>7.425059447996318e-05</v>
+        <v>8.119364736103307e-09</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.48251808443456e-06</v>
+        <v>1.408497762867e-08</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.263477472297382e-05</v>
+        <v>2.898385886851429e-08</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001153218981926329</v>
+        <v>2.615611016665298e-08</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.592326018202584e-05</v>
+        <v>4.174741441431706e-09</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.506295565282926e-05</v>
+        <v>2.020626777010648e-09</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.854403636680217e-06</v>
+        <v>3.31525185082171e-09</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0001331001549260691</v>
+        <v>3.334072928851128e-08</v>
       </c>
       <c r="CF10" t="n">
-        <v>8.688552770763636e-05</v>
+        <v>5.363168242844552e-10</v>
       </c>
       <c r="CG10" t="n">
-        <v>4.303665991756134e-05</v>
+        <v>2.119555375657001e-08</v>
       </c>
       <c r="CH10" t="n">
-        <v>3.592217763070948e-05</v>
+        <v>8.925858274722032e-09</v>
       </c>
       <c r="CI10" t="n">
-        <v>5.752530705649406e-05</v>
+        <v>1.209637190413559e-08</v>
       </c>
       <c r="CJ10" t="n">
-        <v>9.041703378898092e-06</v>
+        <v>5.95236349099082e-09</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.180052549898392e-05</v>
+        <v>3.239888135553315e-09</v>
       </c>
       <c r="CL10" t="n">
-        <v>8.330802666023374e-05</v>
+        <v>7.768132803676053e-09</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0001084053801605478</v>
+        <v>3.016852190285135e-08</v>
       </c>
       <c r="CN10" t="n">
-        <v>7.376651410595514e-06</v>
+        <v>5.78443710708143e-08</v>
       </c>
       <c r="CO10" t="n">
-        <v>4.710099528892897e-05</v>
+        <v>4.063511482854665e-08</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0002288121759193018</v>
+        <v>2.777824903432702e-08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0001605810248292983</v>
+        <v>1.656344572609214e-08</v>
       </c>
       <c r="CR10" t="n">
-        <v>3.339171598781832e-06</v>
+        <v>3.309294172026966e-09</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0001385977957397699</v>
+        <v>2.004446741921129e-08</v>
       </c>
       <c r="CT10" t="n">
-        <v>1.061593047779752e-05</v>
+        <v>1.517182468546707e-08</v>
       </c>
       <c r="CU10" t="n">
-        <v>2.013714401982725e-05</v>
+        <v>1.590154452557613e-09</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.00348570413189e-05</v>
+        <v>6.645742178790215e-09</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0001238533877767622</v>
+        <v>3.097022727160947e-08</v>
       </c>
       <c r="CX10" t="n">
-        <v>7.741260924376547e-05</v>
+        <v>2.140103649850289e-09</v>
       </c>
       <c r="CY10" t="n">
-        <v>8.831071318127215e-05</v>
+        <v>2.496254047912316e-08</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.90450911456719e-05</v>
+        <v>1.393058557397353e-08</v>
       </c>
       <c r="DA10" t="n">
-        <v>6.611374556086957e-05</v>
+        <v>1.313000375091633e-08</v>
       </c>
       <c r="DB10" t="n">
-        <v>3.351533086970448e-05</v>
+        <v>7.420479786190981e-09</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.561449582572095e-05</v>
+        <v>5.308613992838218e-09</v>
       </c>
       <c r="DD10" t="n">
-        <v>6.999034667387605e-05</v>
+        <v>7.706343119195935e-09</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0001150224852608517</v>
+        <v>2.103892171589905e-08</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.244755498599261e-05</v>
+        <v>7.02537494845501e-09</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001841448683990166</v>
+        <v>1.192005161243515e-08</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0003665554977487773</v>
+        <v>1.666330007310535e-08</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0001854106085374951</v>
+        <v>1.433045859755566e-08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>5.833333489135839e-05</v>
+        <v>3.853373087281398e-08</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.307834776933305e-05</v>
+        <v>2.230682971671172e-09</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.252393647329882e-05</v>
+        <v>3.551821237124386e-08</v>
       </c>
       <c r="DM10" t="n">
-        <v>5.244263593340293e-05</v>
+        <v>1.881534572589771e-08</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.465237983211409e-05</v>
+        <v>1.187629994348072e-09</v>
       </c>
       <c r="DO10" t="n">
-        <v>5.58178435312584e-05</v>
+        <v>1.96337488489462e-08</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.229524635476992e-05</v>
+        <v>3.68342334411409e-09</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.94185213331366e-06</v>
+        <v>7.199781215661005e-09</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.137349555501714e-05</v>
+        <v>9.509620646497297e-09</v>
       </c>
       <c r="DS10" t="n">
-        <v>3.403044684091583e-05</v>
+        <v>1.25348860180452e-08</v>
       </c>
       <c r="DT10" t="n">
-        <v>4.019196057925001e-05</v>
+        <v>2.00063485777946e-08</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.442110533389496e-05</v>
+        <v>2.099242202291407e-08</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.000140952950459905</v>
+        <v>7.457034989499789e-09</v>
       </c>
       <c r="DW10" t="n">
-        <v>4.905150854028761e-05</v>
+        <v>1.772582081116525e-11</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.075417281361297e-05</v>
+        <v>2.41963826752567e-09</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0001672529033385217</v>
+        <v>2.239278629190267e-08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.773868098098319e-05</v>
+        <v>2.170001067725025e-08</v>
       </c>
       <c r="EA10" t="n">
-        <v>1.101516591006657e-05</v>
+        <v>1.779172720262068e-08</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0001456696190871298</v>
+        <v>9.783409637975637e-09</v>
       </c>
       <c r="EC10" t="n">
-        <v>4.394003190100193e-05</v>
+        <v>6.78931666442395e-09</v>
       </c>
       <c r="ED10" t="n">
-        <v>1.082849394151708e-05</v>
+        <v>3.419104643853643e-08</v>
       </c>
       <c r="EE10" t="n">
-        <v>1.900482675409876e-05</v>
+        <v>1.060667731422882e-08</v>
       </c>
       <c r="EF10" t="n">
-        <v>2.486300945747644e-05</v>
+        <v>6.983992939524342e-09</v>
       </c>
       <c r="EG10" t="n">
-        <v>9.481518645770848e-05</v>
+        <v>1.191015552848285e-08</v>
       </c>
       <c r="EH10" t="n">
-        <v>4.222993084113114e-05</v>
+        <v>1.361071966243799e-08</v>
       </c>
       <c r="EI10" t="n">
-        <v>3.895456393365748e-05</v>
+        <v>2.083044314815652e-08</v>
       </c>
       <c r="EJ10" t="n">
-        <v>5.754586891271174e-05</v>
+        <v>1.346208389207959e-08</v>
       </c>
       <c r="EK10" t="n">
-        <v>5.185158806852996e-05</v>
+        <v>1.166659391316216e-08</v>
       </c>
       <c r="EL10" t="n">
-        <v>6.80599914630875e-05</v>
+        <v>1.002868277311109e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>1.335316119366325e-05</v>
+        <v>3.430265849146963e-09</v>
       </c>
       <c r="EN10" t="n">
-        <v>3.964611460105516e-05</v>
+        <v>2.3111472735593e-09</v>
       </c>
       <c r="EO10" t="n">
-        <v>1.718314160825685e-05</v>
+        <v>8.191545219915497e-10</v>
       </c>
       <c r="EP10" t="n">
-        <v>5.134349339641631e-05</v>
+        <v>1.779425673475998e-08</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0001020425042952411</v>
+        <v>9.169026427002791e-09</v>
       </c>
       <c r="ER10" t="n">
-        <v>4.058163540321402e-06</v>
+        <v>6.356848381017244e-09</v>
       </c>
       <c r="ES10" t="n">
-        <v>5.477810191223398e-05</v>
+        <v>9.616952567625958e-09</v>
       </c>
       <c r="ET10" t="n">
-        <v>2.386190681136213e-05</v>
+        <v>8.398944317811186e-10</v>
       </c>
       <c r="EU10" t="n">
-        <v>2.640672755660489e-05</v>
+        <v>6.557586917921299e-09</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0001719381689326838</v>
+        <v>2.003338295253343e-08</v>
       </c>
       <c r="EW10" t="n">
-        <v>3.343744901940227e-05</v>
+        <v>1.64360294263588e-08</v>
       </c>
       <c r="EX10" t="n">
-        <v>1.020289710140787e-05</v>
+        <v>4.279415932728625e-09</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.000114277056127321</v>
+        <v>3.644189661144992e-08</v>
       </c>
       <c r="EZ10" t="n">
-        <v>6.325986032607034e-05</v>
+        <v>3.284323701890912e-09</v>
       </c>
       <c r="FA10" t="n">
-        <v>5.194058394408785e-05</v>
+        <v>2.504904017541776e-08</v>
       </c>
       <c r="FB10" t="n">
-        <v>2.857536674127914e-05</v>
+        <v>3.341504628551206e-09</v>
       </c>
       <c r="FC10" t="n">
-        <v>5.933519059908576e-05</v>
+        <v>1.00655945800554e-08</v>
       </c>
       <c r="FD10" t="n">
-        <v>3.252560418331996e-05</v>
+        <v>1.876256483512861e-09</v>
       </c>
       <c r="FE10" t="n">
-        <v>4.695109055319335e-06</v>
+        <v>8.176114008051627e-09</v>
       </c>
       <c r="FF10" t="n">
-        <v>9.675423643784598e-05</v>
+        <v>1.594638310287166e-09</v>
       </c>
       <c r="FG10" t="n">
-        <v>7.183413254097104e-05</v>
+        <v>4.058376135152031e-10</v>
       </c>
       <c r="FH10" t="n">
-        <v>5.431351382867433e-06</v>
+        <v>2.281555566696625e-08</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0001631984632695094</v>
+        <v>7.548562663828307e-09</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0001300989097217098</v>
+        <v>1.656214188017202e-08</v>
       </c>
       <c r="FK10" t="n">
-        <v>8.872394573700149e-06</v>
+        <v>5.871596986395389e-09</v>
       </c>
       <c r="FL10" t="n">
-        <v>8.242054173024371e-05</v>
+        <v>2.629265694054084e-09</v>
       </c>
       <c r="FM10" t="n">
-        <v>6.359712278936058e-05</v>
+        <v>2.562925871529842e-09</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0001513965835329145</v>
+        <v>5.744231312831971e-09</v>
       </c>
       <c r="FO10" t="n">
-        <v>8.226285717682913e-05</v>
+        <v>2.227750250938243e-08</v>
       </c>
       <c r="FP10" t="n">
-        <v>6.330055839498527e-06</v>
+        <v>7.768561793852768e-09</v>
       </c>
       <c r="FQ10" t="n">
-        <v>6.854803359601647e-06</v>
+        <v>3.858885122554057e-08</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.630971332313493e-05</v>
+        <v>2.859520265019455e-08</v>
       </c>
       <c r="FS10" t="n">
-        <v>3.899420335073955e-05</v>
+        <v>9.187758109874267e-09</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0001788678055163473</v>
+        <v>6.178879630169831e-08</v>
       </c>
       <c r="FU10" t="n">
-        <v>2.205050986958668e-05</v>
+        <v>2.179457148088204e-08</v>
       </c>
       <c r="FV10" t="n">
-        <v>7.429991092067212e-05</v>
+        <v>2.563816181577749e-08</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0001380424801027402</v>
+        <v>7.824686676372039e-09</v>
       </c>
       <c r="FX10" t="n">
-        <v>8.023774717003107e-05</v>
+        <v>9.057631089604001e-09</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0001966716081369668</v>
+        <v>3.932036474196821e-09</v>
       </c>
       <c r="FZ10" t="n">
-        <v>6.744666461599991e-05</v>
+        <v>1.69718950004949e-09</v>
       </c>
       <c r="GA10" t="n">
-        <v>1.542712925584055e-05</v>
+        <v>2.699921175519648e-08</v>
       </c>
       <c r="GB10" t="n">
-        <v>1.809133755159564e-05</v>
+        <v>1.611998179384955e-08</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.000228704055189155</v>
+        <v>2.648462071874746e-08</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0001018365655909292</v>
+        <v>4.374267703610712e-08</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.000236850100918673</v>
+        <v>3.155920325070838e-08</v>
       </c>
       <c r="GF10" t="n">
-        <v>3.067612851737067e-05</v>
+        <v>2.066321558302775e-10</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0001061377770383842</v>
+        <v>1.766746304809885e-09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.329311872832477e-05</v>
+        <v>7.737531860889379e-13</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01211751904338598</v>
+        <v>3.737972930316358e-13</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003940300666727126</v>
+        <v>4.069871067761965e-13</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004349670372903347</v>
+        <v>2.698335803928698e-13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003499573329463601</v>
+        <v>4.483945766770026e-13</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006845882628113031</v>
+        <v>2.865578325843277e-13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0006010947399772704</v>
+        <v>8.486116540376565e-13</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002911643357947469</v>
+        <v>1.605479529702414e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00221163802780211</v>
+        <v>8.461746386044522e-13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001111095887608826</v>
+        <v>5.607617235142692e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01254316419363022</v>
+        <v>5.913394773848779e-13</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001285430160351098</v>
+        <v>4.91871409054323e-13</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002815929474309087</v>
+        <v>6.618952348019791e-13</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0007975160260684788</v>
+        <v>3.390328111568114e-13</v>
       </c>
       <c r="O11" t="n">
-        <v>0.005510240793228149</v>
+        <v>2.361641156072014e-13</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0007586004212498665</v>
+        <v>2.175371292606129e-13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005135377869009972</v>
+        <v>1.917900083539537e-12</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002188067184761167</v>
+        <v>3.277091868269383e-13</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0006212783046066761</v>
+        <v>6.672004528723852e-13</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0009730271412990987</v>
+        <v>8.500758690715982e-13</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0003689922741614282</v>
+        <v>1.190518630943618e-13</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0006241302471607924</v>
+        <v>3.546690935732344e-14</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001687036594375968</v>
+        <v>1.744289256219375e-13</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0008210654486902058</v>
+        <v>3.109915753737869e-13</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.334724144428037e-05</v>
+        <v>1.197090386886868e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001383109600283206</v>
+        <v>9.112614227655205e-15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001079214969649911</v>
+        <v>8.055482279487047e-13</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0007853680290281773</v>
+        <v>5.907195847927593e-13</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0007895072922110558</v>
+        <v>1.884213000468565e-13</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001010060892440379</v>
+        <v>3.102773842977163e-13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0002243953786091879</v>
+        <v>3.343328489491953e-13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0008102504070848227</v>
+        <v>2.34646340985939e-13</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0005723332869820297</v>
+        <v>7.330862262719395e-13</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0006899619475007057</v>
+        <v>1.368160820096678e-14</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.001273487927392125</v>
+        <v>2.920286354315266e-14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0001856736489571631</v>
+        <v>5.250573738811715e-13</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001124759088270366</v>
+        <v>4.731419249448532e-13</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001752340816892684</v>
+        <v>3.125904483175512e-13</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001205057371407747</v>
+        <v>6.663750497584719e-13</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.88940635882318e-05</v>
+        <v>1.920953630538125e-13</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0002821257221512496</v>
+        <v>4.127776679491157e-13</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0009072715765796602</v>
+        <v>1.231473419332357e-13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0003789147885981947</v>
+        <v>1.345378344320969e-14</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0003538738237693906</v>
+        <v>6.119537927611052e-13</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0008093081996776164</v>
+        <v>3.758191674529954e-13</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001473653130233288</v>
+        <v>1.303249229454156e-13</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.007530737202614546</v>
+        <v>9.274866031444562e-13</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.001360441790893674</v>
+        <v>6.073359588680549e-13</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.740643347147852e-05</v>
+        <v>9.34036173600751e-14</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.000812411424703896</v>
+        <v>6.642765764536263e-13</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003421674249693751</v>
+        <v>7.80582304522881e-13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.001758421421982348</v>
+        <v>1.554887674778266e-13</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0006730223540216684</v>
+        <v>1.183087509253403e-14</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0009221249492838979</v>
+        <v>7.529255539352742e-14</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0001249785418622196</v>
+        <v>2.098265354869011e-12</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.00303410179913044</v>
+        <v>1.456811884667508e-12</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001202126382850111</v>
+        <v>6.793039438249271e-13</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.776005077175796e-06</v>
+        <v>6.952427457525279e-14</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.003373262006789446</v>
+        <v>1.317622443444688e-12</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.002386102685704827</v>
+        <v>9.818650883661184e-13</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0003345111617818475</v>
+        <v>6.081292695976626e-14</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0001787789660738781</v>
+        <v>1.362023124493184e-12</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.001199216931127012</v>
+        <v>1.952951038733386e-12</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.001083312323316932</v>
+        <v>2.099555067563291e-13</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.001730466959998012</v>
+        <v>4.716345586644466e-13</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0007570735178887844</v>
+        <v>2.541227861821427e-13</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0009028022177517414</v>
+        <v>8.08511298275999e-13</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0007798331207595766</v>
+        <v>1.6379101850858e-13</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0003315884969197214</v>
+        <v>6.025863944110477e-13</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.001084886840544641</v>
+        <v>1.051418880345517e-13</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0003994874132331461</v>
+        <v>2.941486572545504e-13</v>
       </c>
       <c r="BT11" t="n">
-        <v>2.015347126871347e-05</v>
+        <v>5.120163190999727e-13</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.000722019060049206</v>
+        <v>1.086209464387644e-12</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.004823270253837109</v>
+        <v>9.62036114833531e-13</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0001415858278051019</v>
+        <v>2.126229693612952e-13</v>
       </c>
       <c r="BX11" t="n">
-        <v>8.437526412308216e-05</v>
+        <v>9.990069752344177e-13</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.593640187522396e-05</v>
+        <v>5.199208847738584e-14</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001211707131005824</v>
+        <v>4.136276553472901e-13</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.213501572143286e-05</v>
+        <v>2.063366296399527e-13</v>
       </c>
       <c r="CB11" t="n">
-        <v>8.331699064001441e-07</v>
+        <v>1.212148599809976e-13</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.001097905798815191</v>
+        <v>2.807580556929423e-13</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.00015837381943129</v>
+        <v>2.177759654466843e-14</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.002110273810103536</v>
+        <v>1.445283102181547e-13</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.000455076398793608</v>
+        <v>2.852487804337958e-14</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0006296982173807919</v>
+        <v>1.428099175374009e-13</v>
       </c>
       <c r="CH11" t="n">
-        <v>4.864010770688765e-05</v>
+        <v>3.041449470747581e-13</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0009525448549538851</v>
+        <v>1.723681825526943e-13</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001071666018106043</v>
+        <v>4.912345215931507e-14</v>
       </c>
       <c r="CK11" t="n">
-        <v>9.589161345502362e-05</v>
+        <v>2.52313564464389e-14</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0006587660755030811</v>
+        <v>1.160927636575243e-13</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.002590538235381246</v>
+        <v>2.333501772887325e-13</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.001550501096062362</v>
+        <v>3.706236706424448e-14</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0003581047640182078</v>
+        <v>6.035428233575058e-13</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.003788669593632221</v>
+        <v>2.750720658195593e-13</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001203255262225866</v>
+        <v>1.158689897501342e-12</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.001043929602019489</v>
+        <v>1.438382697454763e-13</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.002848129952326417</v>
+        <v>1.192783393756669e-12</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.002129517262801528</v>
+        <v>5.685514179679801e-14</v>
       </c>
       <c r="CU11" t="n">
-        <v>7.728645869065076e-05</v>
+        <v>8.551930864852952e-13</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001106580020859838</v>
+        <v>1.127253943401102e-13</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.001929815858602524</v>
+        <v>1.399383809785187e-13</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0004693424853030592</v>
+        <v>9.164438413873655e-14</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001098996377550066</v>
+        <v>2.128333858979203e-13</v>
       </c>
       <c r="CZ11" t="n">
-        <v>6.998656772339018e-06</v>
+        <v>2.800279539499906e-13</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0009879774879664183</v>
+        <v>1.783056802250396e-13</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0009725064155645669</v>
+        <v>1.482743235917822e-13</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.000463734962977469</v>
+        <v>5.591655814047268e-14</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0005482718115672469</v>
+        <v>1.350315258913382e-13</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0008355312747880816</v>
+        <v>4.576020009965098e-13</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.002602550201117992</v>
+        <v>1.056654438426341e-12</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.000561626860871911</v>
+        <v>1.164292295387226e-12</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.002668125322088599</v>
+        <v>1.862523807058536e-16</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004607160575687885</v>
+        <v>1.945551196275846e-13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003385888878256083</v>
+        <v>4.219038584208495e-13</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0009518176084384322</v>
+        <v>3.888959466957775e-13</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0008955922676250339</v>
+        <v>8.873738332679237e-13</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.002511273138225079</v>
+        <v>5.721078450392214e-13</v>
       </c>
       <c r="DN11" t="n">
-        <v>2.833877806551754e-05</v>
+        <v>4.838240268492666e-13</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0003189877606928349</v>
+        <v>3.950348620267163e-13</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001715126796625555</v>
+        <v>7.571745422492449e-14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1.147971488535404e-06</v>
+        <v>1.563703322642745e-13</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.001564352889545262</v>
+        <v>5.905061595951056e-13</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001588365063071251</v>
+        <v>4.416400242474722e-13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.001618763315491378</v>
+        <v>2.177871733866424e-13</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0003304823476355523</v>
+        <v>2.376100076244281e-13</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.000285403075395152</v>
+        <v>8.476308305423175e-13</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002397906209807843</v>
+        <v>2.631702906812083e-13</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.001088534016162157</v>
+        <v>1.009092711733856e-13</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0002184428740292788</v>
+        <v>5.730078954727102e-13</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001656199106946588</v>
+        <v>2.257320713813446e-13</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0006982302293181419</v>
+        <v>8.923758542007942e-13</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.001527530374005437</v>
+        <v>2.338400198302615e-13</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0007526238914579153</v>
+        <v>7.274173125827732e-13</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001399914734065533</v>
+        <v>5.994841125248063e-13</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.002094349823892117</v>
+        <v>7.316041219021518e-13</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0003664171963464469</v>
+        <v>3.940619261021822e-13</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.002389004919677973</v>
+        <v>2.214938844315173e-13</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.000330849172314629</v>
+        <v>9.016758558333046e-14</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0002996408438775688</v>
+        <v>2.460451818415282e-14</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0001555975759401917</v>
+        <v>2.287494737900075e-13</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0005136543186381459</v>
+        <v>4.666589922645847e-13</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.000946743122767657</v>
+        <v>3.933692293341812e-13</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0007067985134199262</v>
+        <v>1.58885518674115e-13</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0004189230385236442</v>
+        <v>1.192326673591509e-13</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0004399690078571439</v>
+        <v>3.793287027802766e-13</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.00117974414024502</v>
+        <v>1.006546462931773e-13</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0001235117088072002</v>
+        <v>1.064902154087818e-13</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0009481466840952635</v>
+        <v>1.098711101482977e-13</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001010357751511037</v>
+        <v>6.064363421154351e-13</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001096007414162159</v>
+        <v>3.096420960347485e-13</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001952759455889463</v>
+        <v>3.07479817432052e-13</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001796678290702403</v>
+        <v>7.411793618086748e-13</v>
       </c>
       <c r="EW11" t="n">
-        <v>1.360940223094076e-05</v>
+        <v>1.225757505479014e-13</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0003037333372049034</v>
+        <v>3.989565161522865e-14</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001792480354197323</v>
+        <v>1.265172049156466e-13</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.000129613617900759</v>
+        <v>9.48514135073672e-14</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0002987584739457816</v>
+        <v>3.116444819220576e-13</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0001568506850162521</v>
+        <v>3.291926464494416e-13</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0009969531092792749</v>
+        <v>2.240622780629725e-13</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001428265357390046</v>
+        <v>1.149937756779115e-13</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.000179568407475017</v>
+        <v>1.693820864817619e-13</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0009545499924570322</v>
+        <v>9.494850381191328e-14</v>
       </c>
       <c r="FG11" t="n">
-        <v>8.191517554223537e-05</v>
+        <v>1.742733019526044e-14</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0001894342130981386</v>
+        <v>3.321955341015204e-13</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0009259796934202313</v>
+        <v>3.28342116950181e-13</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.002289607655256987</v>
+        <v>6.320266033622846e-13</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0002951954083982855</v>
+        <v>3.000349805843544e-13</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.001010761130601168</v>
+        <v>6.569750169230226e-13</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.00119912950322032</v>
+        <v>9.763567856762786e-14</v>
       </c>
       <c r="FN11" t="n">
-        <v>6.54074246995151e-05</v>
+        <v>1.6132467540661e-14</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0001346072240266949</v>
+        <v>1.414239602162692e-12</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.001395473955199122</v>
+        <v>1.465504584005628e-12</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.002030644100159407</v>
+        <v>2.797938204908423e-14</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0008010659948922694</v>
+        <v>2.000832225595994e-13</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001271272427402437</v>
+        <v>1.536130922984158e-12</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.000356800330337137</v>
+        <v>2.05631388652816e-12</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0007976656779646873</v>
+        <v>9.259132631618539e-14</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001543139573186636</v>
+        <v>7.835458627411529e-14</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0006171116256155074</v>
+        <v>1.873195175361442e-12</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0001776165299816057</v>
+        <v>6.60353607732922e-13</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001910380320623517</v>
+        <v>4.064234842768299e-13</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0005219446611590683</v>
+        <v>4.76240249493165e-13</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001908355479827151</v>
+        <v>9.374317728322312e-13</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0003137454041279852</v>
+        <v>5.453626374281317e-13</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0002022025728365406</v>
+        <v>1.427134913066855e-13</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0007604581769555807</v>
+        <v>3.695420163450647e-13</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001963504124432802</v>
+        <v>6.449292055260569e-13</v>
       </c>
       <c r="GF11" t="n">
-        <v>8.793655433692038e-05</v>
+        <v>4.615264876002556e-13</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0006328023737296462</v>
+        <v>3.008640157755454e-13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.862419594544917e-05</v>
+        <v>1.764493262612632e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>7.457400351995602e-05</v>
+        <v>5.389575719050299e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>1.216825694427826e-05</v>
+        <v>4.601302006079777e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>4.955893746227957e-05</v>
+        <v>3.704718665176188e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>2.936254713858943e-05</v>
+        <v>1.098557333989447e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>2.265260081912857e-05</v>
+        <v>4.206208359391894e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>4.848541266255779e-06</v>
+        <v>1.1609085248665e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.191408268321538e-06</v>
+        <v>1.447421027478413e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.346900345173708e-07</v>
+        <v>8.413718333155629e-11</v>
       </c>
       <c r="J12" t="n">
-        <v>2.690171095309779e-05</v>
+        <v>1.032173013726378e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>5.619438161375001e-05</v>
+        <v>4.683873200406197e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>1.078183322533732e-05</v>
+        <v>5.06046760051504e-09</v>
       </c>
       <c r="M12" t="n">
-        <v>3.479659062577412e-05</v>
+        <v>6.153899789751449e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.12967094941996e-05</v>
+        <v>3.365105172292715e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.99778364226222e-05</v>
+        <v>4.450133062050554e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.144471843872452e-05</v>
+        <v>9.107168352784356e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.642790266487282e-05</v>
+        <v>7.125401602081638e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>4.641871328203706e-06</v>
+        <v>5.375408562713346e-09</v>
       </c>
       <c r="S12" t="n">
-        <v>1.212355073221261e-06</v>
+        <v>4.718045509832791e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>1.40339234349085e-05</v>
+        <v>6.940888752637875e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>6.941762876522262e-06</v>
+        <v>2.215147176798382e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>6.269746791076614e-06</v>
+        <v>2.78230083416986e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.177176727651386e-05</v>
+        <v>1.31601236574852e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>9.846249668044038e-06</v>
+        <v>1.558791318245767e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.575371425133198e-05</v>
+        <v>1.875507926740738e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.424473783932626e-06</v>
+        <v>1.057560439221561e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.325637003901647e-05</v>
+        <v>2.916775709849162e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.973341335949954e-06</v>
+        <v>2.426376433106725e-09</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.649121825015754e-06</v>
+        <v>1.433671581452245e-08</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.769640327140223e-06</v>
+        <v>1.600166665838287e-09</v>
       </c>
       <c r="AE12" t="n">
-        <v>7.805710993125103e-06</v>
+        <v>1.828730411546076e-08</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.297667591250502e-06</v>
+        <v>8.733382905745657e-09</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.484690627279633e-07</v>
+        <v>3.076577215210818e-08</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.884843737178016e-06</v>
+        <v>2.421101097382916e-09</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.669283392402576e-06</v>
+        <v>2.870707582758314e-08</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.039535106883704e-07</v>
+        <v>4.800867259291408e-09</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.11477866084897e-05</v>
+        <v>5.757367027570126e-09</v>
       </c>
       <c r="AL12" t="n">
-        <v>8.590949619247112e-06</v>
+        <v>8.788092031863926e-09</v>
       </c>
       <c r="AM12" t="n">
-        <v>5.220304046815727e-06</v>
+        <v>2.880398497495662e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.63072615780402e-06</v>
+        <v>1.528852422438831e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.6922465369571e-06</v>
+        <v>1.916684766456456e-08</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.622328108576767e-07</v>
+        <v>1.700334451015806e-08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.043639248469844e-06</v>
+        <v>3.312119023490823e-09</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.126952146383701e-06</v>
+        <v>7.214254749143834e-10</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.211708518501837e-06</v>
+        <v>2.10030814962181e-09</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.119330247296602e-06</v>
+        <v>3.504389889386061e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.657187309931032e-05</v>
+        <v>3.426819006335791e-08</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.063150289672194e-07</v>
+        <v>3.835148021380519e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.495740070822649e-05</v>
+        <v>2.124771913969425e-09</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.147958174551604e-06</v>
+        <v>6.684839348736205e-08</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.865283805585932e-06</v>
+        <v>4.369623596289784e-08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.020230001813616e-06</v>
+        <v>3.899371936455509e-09</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.707342542242259e-06</v>
+        <v>9.879407514290506e-09</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.186938516184455e-05</v>
+        <v>1.975624996930492e-09</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.237821288668783e-05</v>
+        <v>6.639133243169226e-09</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.228189194080187e-05</v>
+        <v>2.326634174210085e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.353218587813899e-05</v>
+        <v>9.978027293300329e-09</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.084579707821831e-05</v>
+        <v>2.217324457376435e-08</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.563847374403849e-05</v>
+        <v>5.298656802210644e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.078323839465156e-05</v>
+        <v>6.402666841154314e-09</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.436104184904252e-06</v>
+        <v>3.572094620096777e-09</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.721296575851738e-05</v>
+        <v>2.507115048899777e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.642416464164853e-06</v>
+        <v>3.857847374888479e-09</v>
       </c>
       <c r="BL12" t="n">
-        <v>9.160808986052871e-06</v>
+        <v>2.625565764802218e-09</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.281347067561001e-05</v>
+        <v>1.240752744990914e-08</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.119414537242847e-05</v>
+        <v>3.670904025199206e-09</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.737637482321588e-06</v>
+        <v>1.042397101969073e-08</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.495429377333494e-06</v>
+        <v>2.505897001015001e-08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.322005002497463e-06</v>
+        <v>1.061466026186508e-09</v>
       </c>
       <c r="BR12" t="n">
-        <v>4.485323643166339e-06</v>
+        <v>2.088561545932066e-09</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.570335244759917e-06</v>
+        <v>8.302905030177499e-09</v>
       </c>
       <c r="BT12" t="n">
-        <v>3.850491339107975e-06</v>
+        <v>9.783146737163406e-09</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.161734068475198e-06</v>
+        <v>2.44821851680399e-09</v>
       </c>
       <c r="BV12" t="n">
-        <v>2.184787081205286e-05</v>
+        <v>1.674147220853683e-08</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.465780314902076e-05</v>
+        <v>1.993413967227298e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>6.531337930937298e-06</v>
+        <v>9.46204226082159e-10</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.397894256020663e-06</v>
+        <v>1.195617205240751e-08</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.311674951575696e-07</v>
+        <v>2.523049857927617e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.229178906214656e-05</v>
+        <v>1.727284093533399e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.100358417716052e-06</v>
+        <v>7.314167049798925e-10</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.022620593488682e-06</v>
+        <v>8.845404964041848e-10</v>
       </c>
       <c r="CD12" t="n">
-        <v>6.28686450454552e-07</v>
+        <v>1.760317225318886e-09</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.261862689716509e-05</v>
+        <v>1.840066232716708e-08</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.396497262059711e-06</v>
+        <v>9.128646727418754e-10</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.871934384529595e-06</v>
+        <v>1.279619965544043e-08</v>
       </c>
       <c r="CH12" t="n">
-        <v>2.066597062366782e-06</v>
+        <v>6.686746711892511e-09</v>
       </c>
       <c r="CI12" t="n">
-        <v>7.197412287496263e-06</v>
+        <v>8.614967406117557e-09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.539567278996401e-06</v>
+        <v>4.058772873349881e-09</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.829969733080361e-06</v>
+        <v>1.719848929937484e-09</v>
       </c>
       <c r="CL12" t="n">
-        <v>8.363645974895917e-06</v>
+        <v>6.353611414766647e-09</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.016184978652745e-05</v>
+        <v>1.593337017880003e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>5.619574494630797e-07</v>
+        <v>2.914330465841886e-08</v>
       </c>
       <c r="CO12" t="n">
-        <v>4.344336502981605e-06</v>
+        <v>3.011012950082659e-08</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.714616519166157e-05</v>
+        <v>1.90802822430669e-08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.17337767733261e-05</v>
+        <v>1.472074995234607e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>3.398848093638662e-06</v>
+        <v>8.455178779342987e-10</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.138445895776385e-05</v>
+        <v>1.155910744898847e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>6.499084861388837e-07</v>
+        <v>1.457971254836821e-08</v>
       </c>
       <c r="CU12" t="n">
-        <v>4.306688424549066e-06</v>
+        <v>1.869481680571994e-09</v>
       </c>
       <c r="CV12" t="n">
-        <v>7.449216354871169e-09</v>
+        <v>3.316320107416004e-09</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.144473026215564e-05</v>
+        <v>1.655872239325618e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>8.181626981240697e-06</v>
+        <v>2.09448991483896e-09</v>
       </c>
       <c r="CY12" t="n">
-        <v>7.58598025640822e-06</v>
+        <v>1.541749483635613e-08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.03711965191178e-06</v>
+        <v>1.058181986479667e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>8.725599400349893e-06</v>
+        <v>1.00474748521151e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.18705110657902e-06</v>
+        <v>4.710194012602642e-09</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.535137355152983e-06</v>
+        <v>3.771697620891246e-09</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.152175501483725e-06</v>
+        <v>6.736788904504465e-09</v>
       </c>
       <c r="DE12" t="n">
-        <v>8.957989848568104e-06</v>
+        <v>1.238326774455345e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.588958750493475e-06</v>
+        <v>3.587838914853592e-09</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.615383007447235e-05</v>
+        <v>5.646479728227405e-09</v>
       </c>
       <c r="DH12" t="n">
-        <v>3.280707824160345e-05</v>
+        <v>1.146638428650704e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>1.548215368529782e-05</v>
+        <v>6.39343955555205e-09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>9.342985322291497e-06</v>
+        <v>1.864647636296013e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>1.973439793800935e-06</v>
+        <v>1.076268241195777e-10</v>
       </c>
       <c r="DL12" t="n">
-        <v>1.002393946691882e-05</v>
+        <v>2.216826722190035e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>7.915770765976049e-06</v>
+        <v>1.715659081469312e-08</v>
       </c>
       <c r="DN12" t="n">
-        <v>3.161551376251737e-07</v>
+        <v>2.498516948890028e-10</v>
       </c>
       <c r="DO12" t="n">
-        <v>5.508164576895069e-06</v>
+        <v>1.19611129889563e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>6.962243787711486e-06</v>
+        <v>3.437844675602264e-09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>4.665243068302516e-06</v>
+        <v>6.880203073933444e-09</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.5101663671594e-07</v>
+        <v>4.280782839316544e-09</v>
       </c>
       <c r="DS12" t="n">
-        <v>2.16781177186931e-06</v>
+        <v>6.704766963849806e-09</v>
       </c>
       <c r="DT12" t="n">
-        <v>1.72102795659157e-06</v>
+        <v>1.306526709043965e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>1.816175767999084e-06</v>
+        <v>1.419897532883851e-08</v>
       </c>
       <c r="DV12" t="n">
-        <v>1.201446048071375e-05</v>
+        <v>1.069981214740778e-09</v>
       </c>
       <c r="DW12" t="n">
-        <v>7.798967999406159e-06</v>
+        <v>5.427658322787465e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>7.623175406479277e-06</v>
+        <v>9.605710671323209e-10</v>
       </c>
       <c r="DY12" t="n">
-        <v>1.642202914808877e-05</v>
+        <v>1.776134261888274e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.696227855063626e-06</v>
+        <v>1.324236720279259e-08</v>
       </c>
       <c r="EA12" t="n">
-        <v>5.355751909519313e-06</v>
+        <v>1.31213955256726e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.300307576457271e-05</v>
+        <v>5.328830710027432e-10</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.682077931443928e-06</v>
+        <v>3.887678179381737e-09</v>
       </c>
       <c r="ED12" t="n">
-        <v>1.833296323638933e-06</v>
+        <v>2.476821592267697e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>4.31468436090654e-07</v>
+        <v>8.31498603304226e-09</v>
       </c>
       <c r="EF12" t="n">
-        <v>4.270603312761523e-06</v>
+        <v>4.245230833532787e-09</v>
       </c>
       <c r="EG12" t="n">
-        <v>1.09040174720576e-05</v>
+        <v>3.617139920919499e-09</v>
       </c>
       <c r="EH12" t="n">
-        <v>5.141805104358355e-06</v>
+        <v>6.963461807174554e-09</v>
       </c>
       <c r="EI12" t="n">
-        <v>3.620965344452998e-06</v>
+        <v>1.242776015430991e-08</v>
       </c>
       <c r="EJ12" t="n">
-        <v>3.668984390969854e-06</v>
+        <v>8.161152642571778e-09</v>
       </c>
       <c r="EK12" t="n">
-        <v>6.424852927011671e-06</v>
+        <v>8.109863003369355e-09</v>
       </c>
       <c r="EL12" t="n">
-        <v>6.4732685132185e-06</v>
+        <v>7.100178667229784e-09</v>
       </c>
       <c r="EM12" t="n">
-        <v>3.126942601738847e-06</v>
+        <v>1.888851741682629e-09</v>
       </c>
       <c r="EN12" t="n">
-        <v>3.595436510295258e-06</v>
+        <v>7.560423398444982e-10</v>
       </c>
       <c r="EO12" t="n">
-        <v>2.034901854131022e-06</v>
+        <v>1.093960033671237e-09</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.246132455889892e-06</v>
+        <v>7.972017712631896e-09</v>
       </c>
       <c r="EQ12" t="n">
-        <v>9.99432540993439e-06</v>
+        <v>7.245774646946757e-09</v>
       </c>
       <c r="ER12" t="n">
-        <v>1.079087951438851e-06</v>
+        <v>1.351804446159122e-09</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.033290785329882e-06</v>
+        <v>7.679635594115553e-09</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.408346179232467e-06</v>
+        <v>4.189971036794304e-09</v>
       </c>
       <c r="EU12" t="n">
-        <v>4.430232365848497e-06</v>
+        <v>3.320701935649595e-09</v>
       </c>
       <c r="EV12" t="n">
-        <v>1.980825254577212e-05</v>
+        <v>9.99854954386592e-09</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.708279228296306e-06</v>
+        <v>1.250901426885775e-08</v>
       </c>
       <c r="EX12" t="n">
-        <v>1.653781737331883e-06</v>
+        <v>1.604494315188276e-09</v>
       </c>
       <c r="EY12" t="n">
-        <v>1.059776968759252e-05</v>
+        <v>1.956823325599544e-08</v>
       </c>
       <c r="EZ12" t="n">
-        <v>6.857562311779475e-06</v>
+        <v>2.708615998159303e-09</v>
       </c>
       <c r="FA12" t="n">
-        <v>4.827447810384911e-06</v>
+        <v>1.545549466186458e-08</v>
       </c>
       <c r="FB12" t="n">
-        <v>1.613116069165699e-06</v>
+        <v>2.415797339949677e-09</v>
       </c>
       <c r="FC12" t="n">
-        <v>7.343699053308228e-06</v>
+        <v>6.974754551691831e-09</v>
       </c>
       <c r="FD12" t="n">
-        <v>3.065085820708191e-06</v>
+        <v>1.929670423450602e-09</v>
       </c>
       <c r="FE12" t="n">
-        <v>1.183496010526142e-06</v>
+        <v>4.039969692115619e-09</v>
       </c>
       <c r="FF12" t="n">
-        <v>9.218875675287563e-06</v>
+        <v>1.090484480492648e-09</v>
       </c>
       <c r="FG12" t="n">
-        <v>7.845474101486616e-06</v>
+        <v>9.182422044951011e-10</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.33439516503131e-06</v>
+        <v>1.406402283521402e-08</v>
       </c>
       <c r="FI12" t="n">
-        <v>1.547741339891218e-05</v>
+        <v>8.127685191539058e-09</v>
       </c>
       <c r="FJ12" t="n">
-        <v>1.432182580174413e-05</v>
+        <v>1.007963490451402e-08</v>
       </c>
       <c r="FK12" t="n">
-        <v>2.480612238286994e-06</v>
+        <v>1.886112377391669e-10</v>
       </c>
       <c r="FL12" t="n">
-        <v>9.623974619898945e-06</v>
+        <v>7.399968637855636e-09</v>
       </c>
       <c r="FM12" t="n">
-        <v>3.748784365598112e-06</v>
+        <v>2.29497443271498e-09</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.360024634777801e-05</v>
+        <v>4.893047744758405e-09</v>
       </c>
       <c r="FO12" t="n">
-        <v>9.698734174889978e-06</v>
+        <v>2.801280096775827e-08</v>
       </c>
       <c r="FP12" t="n">
-        <v>1.956377673195675e-06</v>
+        <v>1.526135218199443e-09</v>
       </c>
       <c r="FQ12" t="n">
-        <v>6.257046152313706e-07</v>
+        <v>2.23023430834246e-08</v>
       </c>
       <c r="FR12" t="n">
-        <v>7.069001185300294e-06</v>
+        <v>2.335088211680159e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>7.760952939861454e-06</v>
+        <v>7.950262670419761e-09</v>
       </c>
       <c r="FT12" t="n">
-        <v>1.862791577877942e-05</v>
+        <v>3.077055410471985e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>2.242194057089364e-07</v>
+        <v>1.879975997098882e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>1.054391486832174e-05</v>
+        <v>1.720859010845288e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>6.83273628965253e-06</v>
+        <v>1.4716166063522e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>6.081335413909983e-06</v>
+        <v>8.411154439613711e-09</v>
       </c>
       <c r="FY12" t="n">
-        <v>2.16782464121934e-05</v>
+        <v>2.880057969889549e-09</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.888843694876414e-06</v>
+        <v>5.233104616308992e-09</v>
       </c>
       <c r="GA12" t="n">
-        <v>1.406504338774539e-06</v>
+        <v>2.037635837837115e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>2.259260782011552e-06</v>
+        <v>1.020059148260088e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.960118061106186e-05</v>
+        <v>1.823517337129488e-08</v>
       </c>
       <c r="GD12" t="n">
-        <v>6.693657269352116e-06</v>
+        <v>3.618042399011756e-08</v>
       </c>
       <c r="GE12" t="n">
-        <v>2.288739779032767e-05</v>
+        <v>1.947880434727267e-08</v>
       </c>
       <c r="GF12" t="n">
-        <v>3.778666268772213e-06</v>
+        <v>2.566468371156816e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>9.640801181376446e-06</v>
+        <v>1.682725070395463e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.04699476808309555</v>
+        <v>0.001966496463865042</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6085106730461121</v>
+        <v>0.01196263171732426</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00711769238114357</v>
+        <v>0.003539112629368901</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2915952205657959</v>
+        <v>0.002321475883945823</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007394906133413315</v>
+        <v>0.01230432651937008</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8984547853469849</v>
+        <v>0.03043938241899014</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3849587142467499</v>
+        <v>0.005483538843691349</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4649426341056824</v>
+        <v>0.01683846488595009</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1116535142064095</v>
+        <v>0.001446291105821729</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05693789944052696</v>
+        <v>0.002790483646094799</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5256167650222778</v>
+        <v>0.02311877347528934</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006463614292442799</v>
+        <v>0.00848438311368227</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1218544989824295</v>
+        <v>0.004553257022053003</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1191391944885254</v>
+        <v>0.01697777584195137</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6170530319213867</v>
+        <v>0.03786180913448334</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3803134560585022</v>
+        <v>0.007158294320106506</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2805252373218536</v>
+        <v>0.01507550664246082</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07124023884534836</v>
+        <v>0.008768167346715927</v>
       </c>
       <c r="S13" t="n">
-        <v>0.027482770383358</v>
+        <v>0.00140614272095263</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001663237810134888</v>
+        <v>0.003310910426080227</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04697916284203529</v>
+        <v>0.003400789340957999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1806136816740036</v>
+        <v>0.006444081664085388</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2905216813087463</v>
+        <v>0.003906233003363013</v>
       </c>
       <c r="X13" t="n">
-        <v>0.176475316286087</v>
+        <v>0.00500202365219593</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01070922985672951</v>
+        <v>0.003528267610818148</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.07274609804153442</v>
+        <v>0.005366678349673748</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.1016378775238991</v>
+        <v>0.001387865399010479</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.009797601960599422</v>
+        <v>0.003090532263740897</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04500667750835419</v>
+        <v>0.004229797050356865</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0749971866607666</v>
+        <v>0.001983733614906669</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1155007481575012</v>
+        <v>0.003905354300513864</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1569711118936539</v>
+        <v>0.005176719278097153</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1186982020735741</v>
+        <v>0.00131090625654906</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.007622528821229935</v>
+        <v>0.002898940816521645</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02130997367203236</v>
+        <v>0.0106743760406971</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01248483452945948</v>
+        <v>0.002046651672571898</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.06798657029867172</v>
+        <v>0.002416696865111589</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01751836761832237</v>
+        <v>0.002724415622651577</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.06749983876943588</v>
+        <v>0.001511397771537304</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.08598515391349792</v>
+        <v>0.001003804383799434</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.08975786715745926</v>
+        <v>0.001466037589125335</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1656081676483154</v>
+        <v>0.004840860608965158</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.02650312334299088</v>
+        <v>0.00227508950047195</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.06592234224081039</v>
+        <v>0.004717581439763308</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001992212608456612</v>
+        <v>0.001462267129682004</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.08515187352895737</v>
+        <v>0.003449501236900687</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2968869507312775</v>
+        <v>0.03333741053938866</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.005294982343912125</v>
+        <v>0.003655285574495792</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.2733238935470581</v>
+        <v>0.002188028302043676</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2645565569400787</v>
+        <v>0.00212382385507226</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.6419318318367004</v>
+        <v>0.02538398467004299</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2556039094924927</v>
+        <v>0.003047069534659386</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.1334670931100845</v>
+        <v>0.007775050587952137</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.1616614311933517</v>
+        <v>0.001674533006735146</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.03428122773766518</v>
+        <v>0.004263166803866625</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1154622733592987</v>
+        <v>0.009561422280967236</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.007393550127744675</v>
+        <v>0.0008119477424770594</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.1820558160543442</v>
+        <v>0.007268374320119619</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0638725683093071</v>
+        <v>0.009420327842235565</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.1481054574251175</v>
+        <v>0.004733728244900703</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01191925350576639</v>
+        <v>0.003366895718500018</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01297049317508936</v>
+        <v>0.007639201823621988</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.04803067445755005</v>
+        <v>0.0007019699551165104</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0120941698551178</v>
+        <v>0.002696785144507885</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.104113981127739</v>
+        <v>0.00954331923276186</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01473462209105492</v>
+        <v>0.008211486972868443</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1553873270750046</v>
+        <v>0.004188958555459976</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0603918582201004</v>
+        <v>0.008062919601798058</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.09982394427061081</v>
+        <v>0.00482194172218442</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.08337058126926422</v>
+        <v>0.004912693053483963</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.2437253445386887</v>
+        <v>0.004915633704513311</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.2174748629331589</v>
+        <v>0.004416147246956825</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.007346884347498417</v>
+        <v>0.0001129601732827723</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2427661567926407</v>
+        <v>0.01419816352427006</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.006007738411426544</v>
+        <v>0.002007169183343649</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.1408645212650299</v>
+        <v>0.0002373079769313335</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1214482337236404</v>
+        <v>0.0009726020507514477</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.3313214778900146</v>
+        <v>0.01404429320245981</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01898065581917763</v>
+        <v>0.00487256795167923</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.05115257203578949</v>
+        <v>0.005221287254244089</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.01040492672473192</v>
+        <v>0.0005230822134763002</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.01646341383457184</v>
+        <v>0.000131277774926275</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.09114747494459152</v>
+        <v>0.003360907547175884</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.009127210825681686</v>
+        <v>0.001545583480037749</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0004276745021343231</v>
+        <v>0.0001618630776647478</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.05432271212339401</v>
+        <v>0.003958053886890411</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1456125378608704</v>
+        <v>0.008622598834335804</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.09963318705558777</v>
+        <v>0.004004688002169132</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.1383202373981476</v>
+        <v>0.0009828227339312434</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01855291426181793</v>
+        <v>0.0004217936657369137</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.06389898806810379</v>
+        <v>0.002702017780393362</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0542585626244545</v>
+        <v>0.01075233519077301</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.02378715947270393</v>
+        <v>0.002868317766115069</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.1165481358766556</v>
+        <v>0.004706391133368015</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.2970905005931854</v>
+        <v>0.001560477656312287</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.110188752412796</v>
+        <v>0.001506655244156718</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.009818576276302338</v>
+        <v>0.006585284136235714</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.1204338669776917</v>
+        <v>0.001826735911890864</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.05695029348134995</v>
+        <v>0.002337956568226218</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.00160591397434473</v>
+        <v>0.001034771325066686</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.09487833082675934</v>
+        <v>0.003041364718228579</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01858217641711235</v>
+        <v>0.002649467438459396</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0210321731865406</v>
+        <v>0.0008111076895147562</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.04193668439984322</v>
+        <v>0.004734449088573456</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1824123859405518</v>
+        <v>0.009089772589504719</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.1006607338786125</v>
+        <v>0.002305826870724559</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.1732269078493118</v>
+        <v>0.00188371678814292</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.04838245362043381</v>
+        <v>0.0005060255061835051</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.03328055143356323</v>
+        <v>0.006673099938780069</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.2421386390924454</v>
+        <v>0.0063771759159863</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.04942579194903374</v>
+        <v>0.003009818959981203</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.3218121528625488</v>
+        <v>0.003733061719685793</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06511297821998596</v>
+        <v>0.0003316865768283606</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.1077699959278107</v>
+        <v>0.0007385921198874712</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.1102740094065666</v>
+        <v>0.002820695983245969</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2542385160923004</v>
+        <v>0.006305033341050148</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.1479842662811279</v>
+        <v>0.007609139196574688</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.01413971930742264</v>
+        <v>6.1441445723176e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.003481380641460419</v>
+        <v>0.002483902964740992</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.07011018693447113</v>
+        <v>0.001843333942815661</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.1028220877051353</v>
+        <v>0.004064136650413275</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.09651200473308563</v>
+        <v>0.003508732421323657</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2437379956245422</v>
+        <v>0.005582720506936312</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.114061675965786</v>
+        <v>0.002745486795902252</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.02766820788383484</v>
+        <v>0.002057155128568411</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.01082398183643818</v>
+        <v>0.00728866271674633</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.02705519832670689</v>
+        <v>0.002752532484009862</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01180175133049488</v>
+        <v>0.007119887042790651</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.03351416066288948</v>
+        <v>0.003419292392209172</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01067198161035776</v>
+        <v>8.519482798874378e-05</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.05246668308973312</v>
+        <v>0.002177106216549873</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.02510610967874527</v>
+        <v>0.001869690138846636</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.09090652316808701</v>
+        <v>0.001320302952080965</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0700814425945282</v>
+        <v>0.006204436533153057</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.1403441578149796</v>
+        <v>0.0008920986438170075</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.02004476636648178</v>
+        <v>0.0008870279416441917</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.05087633430957794</v>
+        <v>0.0006305137649178505</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.05740824341773987</v>
+        <v>0.002297410741448402</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.1528827100992203</v>
+        <v>0.00233537401072681</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.07833103835582733</v>
+        <v>0.002906390000134706</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01796372979879379</v>
+        <v>0.00407673604786396</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.04898335412144661</v>
+        <v>0.003705816343426704</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.1472262442111969</v>
+        <v>0.002900706604123116</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.04372202605009079</v>
+        <v>0.0001541937672300264</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.002382539678364992</v>
+        <v>0.001942878821864724</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.07782983779907227</v>
+        <v>0.003145050024613738</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.08143438398838043</v>
+        <v>0.0002664985368028283</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.1338107138872147</v>
+        <v>0.002371200826019049</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01460257545113564</v>
+        <v>0.006997095886617899</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.007858556695282459</v>
+        <v>0.007438358385115862</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.03762096166610718</v>
+        <v>0.004579935222864151</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.2299095541238785</v>
+        <v>0.001583523349836469</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.1690263599157333</v>
+        <v>0.001925587886944413</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.002382721751928329</v>
+        <v>0.001492276904173195</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.07609686255455017</v>
+        <v>0.003849984146654606</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01467488892376423</v>
+        <v>0.001326283207163215</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001023668795824051</v>
+        <v>0.0009801121195778251</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.03689167276024818</v>
+        <v>0.003075036685913801</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1282967180013657</v>
+        <v>0.008921921253204346</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.1202161535620689</v>
+        <v>0.004782454110682011</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.1454712897539139</v>
+        <v>0.001400013687089086</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.03230603784322739</v>
+        <v>0.0007382952026091516</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.002853326499462128</v>
+        <v>0.00335046905092895</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.1173585280776024</v>
+        <v>1.242198050022125e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.02690350636839867</v>
+        <v>0.0003767865709960461</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.07820352911949158</v>
+        <v>0.005011531058698893</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.08088413625955582</v>
+        <v>0.0009527436923235655</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.09304855763912201</v>
+        <v>0.004299202468246222</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.02079672366380692</v>
+        <v>0.00398207176476717</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.08268590271472931</v>
+        <v>0.0009582831989973783</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01121564954519272</v>
+        <v>0.005827124230563641</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.09815074503421783</v>
+        <v>0.002641913946717978</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.1439857333898544</v>
+        <v>0.008714092895388603</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.06893680989742279</v>
+        <v>0.006885468494147062</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.08625209331512451</v>
+        <v>0.007815876975655556</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01629137061536312</v>
+        <v>0.01172491814941168</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.1458102762699127</v>
+        <v>0.001417324179783463</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.05348407849669456</v>
+        <v>0.00104907201603055</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.09929762780666351</v>
+        <v>0.003960459027439356</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.2168488651514053</v>
+        <v>0.006611346267163754</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02263677679002285</v>
+        <v>0.001830200897529721</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.05624157935380936</v>
+        <v>0.00120058108586818</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.06263427436351776</v>
+        <v>0.009048950858414173</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.139314591884613</v>
+        <v>0.002296278486028314</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.4402727782726288</v>
+        <v>0.00840314943343401</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.05385250598192215</v>
+        <v>0.001557460287585855</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.1420992016792297</v>
+        <v>0.00861038826406002</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.09241326153278351</v>
+        <v>0.003001796547323465</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.06258931010961533</v>
+        <v>0.001260445103980601</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.003734592813998461</v>
+        <v>0.04606419429183006</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001207777764648199</v>
+        <v>0.003348800353705883</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0005685239448212087</v>
+        <v>0.03341511636972427</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0002991388610098511</v>
+        <v>0.004025829955935478</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0002817322092596442</v>
+        <v>0.004320818930864334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002890251576900482</v>
+        <v>0.04302346706390381</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0006184986559674144</v>
+        <v>0.004120904020965099</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001121404580771923</v>
+        <v>0.02131956815719604</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0008544462616555393</v>
+        <v>0.01675085723400116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00268512824550271</v>
+        <v>0.0477394126355648</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001109452918171883</v>
+        <v>0.01687920466065407</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003824998857453465</v>
+        <v>0.04541216045618057</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0002469570026732981</v>
+        <v>0.02296044491231441</v>
       </c>
       <c r="N14" t="n">
-        <v>3.976204607170075e-05</v>
+        <v>0.0185459777712822</v>
       </c>
       <c r="O14" t="n">
-        <v>0.002486004726961255</v>
+        <v>0.06464380770921707</v>
       </c>
       <c r="P14" t="n">
-        <v>0.001139584695920348</v>
+        <v>0.009269217029213905</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0008283316856250167</v>
+        <v>0.01186066493391991</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0008517567766830325</v>
+        <v>0.02472237683832645</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0006787461461499333</v>
+        <v>0.005613356828689575</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0007741098525002599</v>
+        <v>0.01276294980198145</v>
       </c>
       <c r="U14" t="n">
-        <v>6.079630111344159e-06</v>
+        <v>0.01413784548640251</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0002024144632741809</v>
+        <v>0.003411917947232723</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0008228833903558552</v>
+        <v>0.003645858028903604</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0007809557137079537</v>
+        <v>0.0008855279302224517</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0002713187714107335</v>
+        <v>0.02085196971893311</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003330201143398881</v>
+        <v>0.00243498245254159</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.69444411364384e-05</v>
+        <v>0.001474449876695871</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0007931838626973331</v>
+        <v>0.006088920868933201</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.091528772842139e-05</v>
+        <v>0.002153716515749693</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001091604717657901</v>
+        <v>0.01054294686764479</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.28438111662399e-05</v>
+        <v>0.01163140870630741</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0001956686319317669</v>
+        <v>0.01656284928321838</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.778921958059072e-05</v>
+        <v>0.002969660330563784</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0001412647106917575</v>
+        <v>0.01419007126241922</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.911861858796328e-05</v>
+        <v>0.005141391884535551</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0005609709769487381</v>
+        <v>0.01156683079898357</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.000528798729646951</v>
+        <v>0.008274540305137634</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0002142779412679374</v>
+        <v>0.006953799165785313</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0004169637686572969</v>
+        <v>4.543550312519073e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001498407800681889</v>
+        <v>0.003731120377779007</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0006701088277623057</v>
+        <v>0.01258392818272114</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.000227137963520363</v>
+        <v>0.002312172437086701</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0001988535077543929</v>
+        <v>0.002250360557809472</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.266896813642234e-05</v>
+        <v>0.008181069046258926</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001020399940898642</v>
+        <v>0.00146351708099246</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.002437495859339833</v>
+        <v>0.008773605339229107</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0006289895391091704</v>
+        <v>0.02152663841843605</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0006414127419702709</v>
+        <v>0.02825151942670345</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0002391015295870602</v>
+        <v>0.002747056540101767</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0001163752167485654</v>
+        <v>0.0207210835069418</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.001238556345924735</v>
+        <v>0.03725716471672058</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0005931774503551424</v>
+        <v>0.003201212733983994</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0002207471407018602</v>
+        <v>0.005965852178633213</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.000332729279762134</v>
+        <v>0.002208920195698738</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0006282441900111735</v>
+        <v>0.02083259262144566</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0004982561804354191</v>
+        <v>0.02125787734985352</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.217059176880866e-05</v>
+        <v>0.0005723265931010246</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.780610419809818e-05</v>
+        <v>0.001118925400078297</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0001631935010664165</v>
+        <v>0.02843339368700981</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001355310319922864</v>
+        <v>0.0107260849326849</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0001148650917457417</v>
+        <v>0.004329868126660585</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.454183802707121e-06</v>
+        <v>0.0007021606434136629</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0007229281472973526</v>
+        <v>0.005904737394303083</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0003428318887017667</v>
+        <v>0.007823052816092968</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.475488094612956e-05</v>
+        <v>0.004550745710730553</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0003066163044422865</v>
+        <v>0.02086888439953327</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.164585723425262e-05</v>
+        <v>0.001178106060251594</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0001189483300549909</v>
+        <v>0.01104887761175632</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.327442078036256e-06</v>
+        <v>0.002549295546486974</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0002329862327314913</v>
+        <v>8.774222806096077e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0002221913455286995</v>
+        <v>0.001855430193245411</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0002005458372877911</v>
+        <v>0.005812479183077812</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.001187929883599281</v>
+        <v>0.005480806808918715</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0002754353336058557</v>
+        <v>0.006768292747437954</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.000561047054361552</v>
+        <v>0.01224642898887396</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.000303790089674294</v>
+        <v>0.0003867140039801598</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0005462762201204896</v>
+        <v>0.008718022145330906</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.001030073151923716</v>
+        <v>0.01848892867565155</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002494020154699683</v>
+        <v>0.01754536107182503</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0002609372895676643</v>
+        <v>0.0007405632059089839</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.737795724300668e-05</v>
+        <v>0.002600227016955614</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0007809242233633995</v>
+        <v>0.01079525891691446</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0005680614267475903</v>
+        <v>0.01422075647860765</v>
       </c>
       <c r="CF14" t="n">
-        <v>8.143654122250155e-05</v>
+        <v>0.01045301556587219</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.844875027425587e-05</v>
+        <v>0.003778610145673156</v>
       </c>
       <c r="CH14" t="n">
-        <v>9.349857282359153e-05</v>
+        <v>0.003518206300213933</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0003163014771416783</v>
+        <v>0.007551918737590313</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0002027834416367114</v>
+        <v>0.002063607098534703</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0003274056361988187</v>
+        <v>0.0002866705763153732</v>
       </c>
       <c r="CL14" t="n">
-        <v>3.080025635426864e-05</v>
+        <v>0.002268079435452819</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0003973106213379651</v>
+        <v>0.005224925465881824</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0009811522904783487</v>
+        <v>0.004595134872943163</v>
       </c>
       <c r="CO14" t="n">
-        <v>4.710799839813262e-05</v>
+        <v>0.004637949168682098</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.000619688828010112</v>
+        <v>0.002206896897405386</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0005995154497213662</v>
+        <v>0.02315555512905121</v>
       </c>
       <c r="CR14" t="n">
-        <v>9.907849016599357e-05</v>
+        <v>0.007331152446568012</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.000164614524692297</v>
+        <v>0.004734175279736519</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0005457806400954723</v>
+        <v>0.01721393130719662</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002940876292996109</v>
+        <v>0.002114314585924149</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0007421079790219665</v>
+        <v>0.01208799798041582</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0006235064938664436</v>
+        <v>0.01007525622844696</v>
       </c>
       <c r="CX14" t="n">
-        <v>5.739946209359914e-05</v>
+        <v>0.01168623939156532</v>
       </c>
       <c r="CY14" t="n">
-        <v>5.130205681780353e-05</v>
+        <v>0.003071008715778589</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.350060407887213e-06</v>
+        <v>0.006335531361401081</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0002357341872993857</v>
+        <v>0.01046576071530581</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001103471295209602</v>
+        <v>0.004817474167793989</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0003565287333913147</v>
+        <v>0.0003166471724398434</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.743190947920084e-05</v>
+        <v>0.002942587016150355</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001636118395254016</v>
+        <v>0.01357110124081373</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0002138067211490124</v>
+        <v>0.02112662419676781</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0002534915402065963</v>
+        <v>0.004871193785220385</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0002056030207313597</v>
+        <v>0.02418074198067188</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001147456467151642</v>
+        <v>0.004411377944052219</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0005392696475610137</v>
+        <v>0.008847297169268131</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0003153375291731209</v>
+        <v>0.005033113993704319</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0006618935149163008</v>
+        <v>0.01994978077709675</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0007693394436500967</v>
+        <v>0.01065598800778389</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0006967692170292139</v>
+        <v>0.007951370440423489</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001826046063797548</v>
+        <v>0.0005568591877818108</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0001733361423248425</v>
+        <v>0.01286003924906254</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0002392480382695794</v>
+        <v>0.0002185872872360051</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.576031642500311e-05</v>
+        <v>0.009383453987538815</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0005701115587726235</v>
+        <v>0.01442060805857182</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0001527168496977538</v>
+        <v>0.01874527335166931</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0002593350945971906</v>
+        <v>0.0008985152235254645</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0003529317036736757</v>
+        <v>0.004858599975705147</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0002980726421810687</v>
+        <v>0.0008871650788933039</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001132479956140742</v>
+        <v>0.01447285804897547</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.000121130928164348</v>
+        <v>0.0209154449403286</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0003406698815524578</v>
+        <v>0.04349097236990929</v>
       </c>
       <c r="EA14" t="n">
-        <v>1.261352736037225e-05</v>
+        <v>0.03607778623700142</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0001138438310590573</v>
+        <v>0.01509766466915607</v>
       </c>
       <c r="EC14" t="n">
-        <v>5.56005907128565e-05</v>
+        <v>0.005871898028999567</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0002814257168211043</v>
+        <v>0.0009888657368719578</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.000494366220664233</v>
+        <v>0.006895071361213923</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0004170929896645248</v>
+        <v>0.003443554043769836</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0005002926918677986</v>
+        <v>0.01114812958985567</v>
       </c>
       <c r="EH14" t="n">
-        <v>3.58741181116784e-06</v>
+        <v>0.01015544775873423</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001493844902142882</v>
+        <v>0.002518096938729286</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.245189923793077e-05</v>
+        <v>0.007219501305371523</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0001408736861776561</v>
+        <v>0.004620645195245743</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0003122860507573932</v>
+        <v>0.002985491650179029</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0001588880259077996</v>
+        <v>0.0007930057472549379</v>
       </c>
       <c r="EN14" t="n">
-        <v>6.156678864499554e-06</v>
+        <v>0.003313574008643627</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0003105473588220775</v>
+        <v>0.006353588774800301</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001097609987482429</v>
+        <v>0.02556031197309494</v>
       </c>
       <c r="EQ14" t="n">
-        <v>1.567017170600593e-05</v>
+        <v>0.001967168878763914</v>
       </c>
       <c r="ER14" t="n">
-        <v>8.334565791301429e-05</v>
+        <v>0.009128028526902199</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0003804145380854607</v>
+        <v>0.0006684692343696952</v>
       </c>
       <c r="ET14" t="n">
-        <v>9.671317820902914e-05</v>
+        <v>0.007966254837810993</v>
       </c>
       <c r="EU14" t="n">
-        <v>7.258354162331671e-05</v>
+        <v>0.01107673719525337</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.000371664937119931</v>
+        <v>0.02577280625700951</v>
       </c>
       <c r="EW14" t="n">
-        <v>9.937626600731164e-05</v>
+        <v>0.003976856358349323</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0006323502166196704</v>
+        <v>0.01081908866763115</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0005759970517829061</v>
+        <v>0.01019180938601494</v>
       </c>
       <c r="EZ14" t="n">
-        <v>1.966179115697742e-05</v>
+        <v>0.008950849995017052</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.000191137456567958</v>
+        <v>0.003445216454565525</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.75580860034097e-05</v>
+        <v>0.004811567720025778</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0002431355242151767</v>
+        <v>0.01215383969247341</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0002465949510224164</v>
+        <v>0.006536798551678658</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0004183685232419521</v>
+        <v>0.001942975679412484</v>
       </c>
       <c r="FF14" t="n">
-        <v>8.448364678770304e-05</v>
+        <v>0.001351952785626054</v>
       </c>
       <c r="FG14" t="n">
-        <v>3.707941141328774e-05</v>
+        <v>0.01844370737671852</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0003130364057142287</v>
+        <v>0.01119749993085861</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0001451380958314985</v>
+        <v>0.008642526343464851</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0004275070386938751</v>
+        <v>0.02087084390223026</v>
       </c>
       <c r="FK14" t="n">
-        <v>7.286892650881782e-05</v>
+        <v>0.01483325101435184</v>
       </c>
       <c r="FL14" t="n">
-        <v>3.011664375662804e-07</v>
+        <v>0.01083356328308582</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0003121381159871817</v>
+        <v>0.01655671373009682</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0004582517722155899</v>
+        <v>0.02569647319614887</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0001637413224671036</v>
+        <v>0.01324581913650036</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0009745701099745929</v>
+        <v>0.006566574797034264</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0001603448909008875</v>
+        <v>0.01783468946814537</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.000194448497495614</v>
+        <v>0.01779135316610336</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.001093660015612841</v>
+        <v>0.02593257091939449</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0004643009742721915</v>
+        <v>0.01006152294576168</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0006287317373789847</v>
+        <v>0.01935798302292824</v>
       </c>
       <c r="FV14" t="n">
-        <v>9.836902609094977e-05</v>
+        <v>0.02718271501362324</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001897149777505547</v>
+        <v>0.007708956021815538</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002316800819244236</v>
+        <v>0.01291314233094454</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0001257205585716292</v>
+        <v>0.009561119601130486</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0003705216222442687</v>
+        <v>0.02178914286196232</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0003500765888020396</v>
+        <v>0.01810315623879433</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001656924723647535</v>
+        <v>0.0005786099936813116</v>
       </c>
       <c r="GC14" t="n">
-        <v>5.427355063147843e-05</v>
+        <v>0.002883910201489925</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0002025959838647395</v>
+        <v>0.001140823820605874</v>
       </c>
       <c r="GE14" t="n">
-        <v>4.688679109676741e-05</v>
+        <v>0.002911257790401578</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001456334139220417</v>
+        <v>0.03014122135937214</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0002153488167095929</v>
+        <v>0.003597588511183858</v>
       </c>
     </row>
   </sheetData>
